--- a/reports/excel/Load_Report.xlsx
+++ b/reports/excel/Load_Report.xlsx
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:22</t>
+    <t>2026-08-20 04:41:24</t>
   </si>
   <si>
     <t>TC-LOAD-002</t>
@@ -409,6 +409,9 @@
     <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 2/5)</t>
   </si>
   <si>
+    <t>0.01s</t>
+  </si>
+  <si>
     <t>TC-LOAD-053</t>
   </si>
   <si>
@@ -427,9 +430,6 @@
     <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 5/5)</t>
   </si>
   <si>
-    <t>0.01s</t>
-  </si>
-  <si>
     <t>TC-LOAD-056</t>
   </si>
   <si>
@@ -496,15 +496,15 @@
     <t>Concurrency: 20 VU Concurrent Feed Requests (Batch Cycle 1/5)</t>
   </si>
   <si>
+    <t>TC-LOAD-067</t>
+  </si>
+  <si>
+    <t>Concurrency: 20 VU Concurrent Feed Requests (Batch Cycle 2/5)</t>
+  </si>
+  <si>
     <t>0.02s</t>
   </si>
   <si>
-    <t>TC-LOAD-067</t>
-  </si>
-  <si>
-    <t>Concurrency: 20 VU Concurrent Feed Requests (Batch Cycle 2/5)</t>
-  </si>
-  <si>
     <t>TC-LOAD-068</t>
   </si>
   <si>
@@ -571,6 +571,12 @@
     <t>Concurrency: 5 VU Concurrent /api/cluster Requests (Batch Cycle 3/5)</t>
   </si>
   <si>
+    <t>2026-08-20 04:41:25</t>
+  </si>
+  <si>
+    <t>0.76s</t>
+  </si>
+  <si>
     <t>TC-LOAD-079</t>
   </si>
   <si>
@@ -625,9 +631,6 @@
     <t>Concurrency: 15 VU Concurrent /api/regions Requests (Batch Cycle 2/5)</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:23</t>
-  </si>
-  <si>
     <t>TC-LOAD-088</t>
   </si>
   <si>
@@ -805,18 +808,12 @@
     <t>Stress: Rapid traffic burst on Settings Page (Burst Round 1/5)</t>
   </si>
   <si>
-    <t>0.03s</t>
-  </si>
-  <si>
     <t>TC-LOAD-117</t>
   </si>
   <si>
     <t>Stress: Rapid traffic burst on Settings Page (Burst Round 2/5)</t>
   </si>
   <si>
-    <t>0.04s</t>
-  </si>
-  <si>
     <t>TC-LOAD-118</t>
   </si>
   <si>
@@ -827,6 +824,9 @@
   </si>
   <si>
     <t>Stress: Rapid traffic burst on Settings Page (Burst Round 4/5)</t>
+  </si>
+  <si>
+    <t>2026-08-20 04:41:26</t>
   </si>
   <si>
     <t>TC-LOAD-120</t>
@@ -5589,18 +5589,18 @@
         <v>27</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>25</v>
@@ -5620,13 +5620,13 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>25</v>
@@ -5646,13 +5646,13 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>25</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>27</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5745,7 +5745,7 @@
         <v>27</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5771,7 +5771,7 @@
         <v>27</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5797,7 +5797,7 @@
         <v>27</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5823,7 +5823,7 @@
         <v>27</v>
       </c>
       <c r="H62" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5875,7 +5875,7 @@
         <v>27</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5901,7 +5901,7 @@
         <v>27</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5927,7 +5927,7 @@
         <v>27</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5953,33 +5953,33 @@
         <v>27</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C68" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="15" t="s">
         <v>162</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F68" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G68" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="H68" s="15" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6005,7 +6005,7 @@
         <v>27</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6031,7 +6031,7 @@
         <v>27</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6057,7 +6057,7 @@
         <v>27</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6083,7 +6083,7 @@
         <v>27</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6135,7 +6135,7 @@
         <v>27</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6161,7 +6161,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
         <v>27</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6239,7 +6239,7 @@
         <v>27</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6262,21 +6262,21 @@
         <v>27</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>13</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>25</v>
@@ -6285,10 +6285,10 @@
         <v>26</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H80" s="15" t="s">
         <v>13</v>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>25</v>
@@ -6311,10 +6311,10 @@
         <v>26</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H81" s="20" t="s">
         <v>13</v>
@@ -6322,13 +6322,13 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>25</v>
@@ -6337,10 +6337,10 @@
         <v>26</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H82" s="15" t="s">
         <v>13</v>
@@ -6348,13 +6348,13 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>25</v>
@@ -6363,24 +6363,24 @@
         <v>26</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B84" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>25</v>
@@ -6389,10 +6389,10 @@
         <v>26</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H84" s="15" t="s">
         <v>13</v>
@@ -6400,13 +6400,13 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B85" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>25</v>
@@ -6415,10 +6415,10 @@
         <v>26</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H85" s="20" t="s">
         <v>13</v>
@@ -6426,13 +6426,13 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B86" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>25</v>
@@ -6441,24 +6441,24 @@
         <v>26</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>25</v>
@@ -6467,24 +6467,24 @@
         <v>26</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B88" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>25</v>
@@ -6493,24 +6493,24 @@
         <v>26</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>25</v>
@@ -6519,24 +6519,24 @@
         <v>26</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B90" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>25</v>
@@ -6545,24 +6545,24 @@
         <v>26</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>25</v>
@@ -6571,24 +6571,24 @@
         <v>26</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B92" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>25</v>
@@ -6597,24 +6597,24 @@
         <v>26</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B93" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>25</v>
@@ -6623,24 +6623,24 @@
         <v>26</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>25</v>
@@ -6649,24 +6649,24 @@
         <v>26</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G94" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B95" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>25</v>
@@ -6675,24 +6675,24 @@
         <v>26</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B96" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>25</v>
@@ -6701,24 +6701,24 @@
         <v>26</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G96" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B97" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>25</v>
@@ -6727,24 +6727,24 @@
         <v>26</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B98" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>25</v>
@@ -6753,24 +6753,24 @@
         <v>26</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H98" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B99" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>25</v>
@@ -6779,24 +6779,24 @@
         <v>26</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B100" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>25</v>
@@ -6805,24 +6805,24 @@
         <v>26</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B101" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>25</v>
@@ -6831,24 +6831,24 @@
         <v>26</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>25</v>
@@ -6857,24 +6857,24 @@
         <v>26</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>25</v>
@@ -6883,24 +6883,24 @@
         <v>26</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>25</v>
@@ -6909,24 +6909,24 @@
         <v>26</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>25</v>
@@ -6935,24 +6935,24 @@
         <v>26</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>25</v>
@@ -6961,24 +6961,24 @@
         <v>26</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6987,24 +6987,24 @@
         <v>26</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -7013,24 +7013,24 @@
         <v>26</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -7039,24 +7039,24 @@
         <v>26</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -7065,10 +7065,10 @@
         <v>26</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H110" s="15" t="s">
         <v>13</v>
@@ -7076,13 +7076,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -7091,10 +7091,10 @@
         <v>26</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H111" s="20" t="s">
         <v>13</v>
@@ -7102,13 +7102,13 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
@@ -7117,24 +7117,24 @@
         <v>26</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
@@ -7143,24 +7143,24 @@
         <v>26</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
@@ -7169,24 +7169,24 @@
         <v>26</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
@@ -7195,10 +7195,10 @@
         <v>26</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H115" s="20" t="s">
         <v>13</v>
@@ -7206,13 +7206,13 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
@@ -7221,24 +7221,24 @@
         <v>26</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
@@ -7247,13 +7247,13 @@
         <v>26</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>263</v>
+        <v>131</v>
       </c>
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7261,7 +7261,7 @@
         <v>264</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C118" s="14" t="s">
         <v>265</v>
@@ -7273,25 +7273,25 @@
         <v>26</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>266</v>
+        <v>131</v>
       </c>
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="B119" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>268</v>
-      </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
       </c>
@@ -7299,25 +7299,25 @@
         <v>26</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C120" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="B120" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C120" s="14" t="s">
-        <v>270</v>
-      </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
       </c>
@@ -7325,13 +7325,13 @@
         <v>26</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7339,7 +7339,7 @@
         <v>271</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C121" s="19" t="s">
         <v>272</v>
@@ -7351,13 +7351,13 @@
         <v>26</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7365,7 +7365,7 @@
         <v>273</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>274</v>
@@ -7377,13 +7377,13 @@
         <v>26</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H122" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7391,7 +7391,7 @@
         <v>275</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C123" s="19" t="s">
         <v>276</v>
@@ -7403,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7417,7 +7417,7 @@
         <v>277</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C124" s="14" t="s">
         <v>278</v>
@@ -7429,13 +7429,13 @@
         <v>26</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7443,7 +7443,7 @@
         <v>279</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C125" s="19" t="s">
         <v>280</v>
@@ -7455,13 +7455,13 @@
         <v>26</v>
       </c>
       <c r="F125" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H125" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7469,7 +7469,7 @@
         <v>281</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C126" s="14" t="s">
         <v>282</v>
@@ -7481,13 +7481,13 @@
         <v>26</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7495,7 +7495,7 @@
         <v>283</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C127" s="19" t="s">
         <v>284</v>
@@ -7507,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="F127" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H127" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7521,7 +7521,7 @@
         <v>285</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C128" s="14" t="s">
         <v>286</v>
@@ -7533,13 +7533,13 @@
         <v>26</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H128" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7547,7 +7547,7 @@
         <v>287</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C129" s="19" t="s">
         <v>288</v>
@@ -7559,13 +7559,13 @@
         <v>26</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H129" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>289</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>290</v>
@@ -7585,13 +7585,13 @@
         <v>26</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H130" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7599,7 +7599,7 @@
         <v>291</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C131" s="19" t="s">
         <v>292</v>
@@ -7611,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="F131" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G131" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H131" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7625,7 +7625,7 @@
         <v>293</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C132" s="14" t="s">
         <v>294</v>
@@ -7637,13 +7637,13 @@
         <v>26</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H132" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7651,7 +7651,7 @@
         <v>295</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C133" s="19" t="s">
         <v>296</v>
@@ -7663,13 +7663,13 @@
         <v>26</v>
       </c>
       <c r="F133" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H133" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>297</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>298</v>
@@ -7689,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7703,7 +7703,7 @@
         <v>299</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C135" s="19" t="s">
         <v>300</v>
@@ -7715,13 +7715,13 @@
         <v>26</v>
       </c>
       <c r="F135" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H135" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7729,7 +7729,7 @@
         <v>301</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C136" s="14" t="s">
         <v>302</v>
@@ -7741,13 +7741,13 @@
         <v>26</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H136" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7755,7 +7755,7 @@
         <v>303</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C137" s="19" t="s">
         <v>304</v>
@@ -7767,13 +7767,13 @@
         <v>26</v>
       </c>
       <c r="F137" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H137" s="20" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>305</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C138" s="14" t="s">
         <v>306</v>
@@ -7793,13 +7793,13 @@
         <v>26</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H138" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7807,7 +7807,7 @@
         <v>307</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C139" s="19" t="s">
         <v>308</v>
@@ -7819,13 +7819,13 @@
         <v>26</v>
       </c>
       <c r="F139" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H139" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
         <v>309</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>310</v>
@@ -7845,13 +7845,13 @@
         <v>26</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7859,7 +7859,7 @@
         <v>311</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C141" s="19" t="s">
         <v>312</v>
@@ -7871,13 +7871,13 @@
         <v>26</v>
       </c>
       <c r="F141" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H141" s="20" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7885,7 +7885,7 @@
         <v>313</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C142" s="14" t="s">
         <v>314</v>
@@ -7897,10 +7897,10 @@
         <v>26</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H142" s="15" t="s">
         <v>13</v>
@@ -7911,7 +7911,7 @@
         <v>315</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C143" s="19" t="s">
         <v>316</v>
@@ -7923,13 +7923,13 @@
         <v>26</v>
       </c>
       <c r="F143" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H143" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7937,7 +7937,7 @@
         <v>317</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>318</v>
@@ -7949,13 +7949,13 @@
         <v>26</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7963,7 +7963,7 @@
         <v>319</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C145" s="19" t="s">
         <v>320</v>
@@ -7975,13 +7975,13 @@
         <v>26</v>
       </c>
       <c r="F145" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H145" s="20" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7989,7 +7989,7 @@
         <v>321</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>322</v>
@@ -8001,13 +8001,13 @@
         <v>26</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8015,7 +8015,7 @@
         <v>323</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C147" s="19" t="s">
         <v>324</v>
@@ -8027,13 +8027,13 @@
         <v>26</v>
       </c>
       <c r="F147" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H147" s="20" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8041,7 +8041,7 @@
         <v>325</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C148" s="14" t="s">
         <v>326</v>
@@ -8053,13 +8053,13 @@
         <v>26</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8067,7 +8067,7 @@
         <v>327</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C149" s="19" t="s">
         <v>328</v>
@@ -8079,13 +8079,13 @@
         <v>26</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H149" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>329</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C150" s="14" t="s">
         <v>330</v>
@@ -8105,13 +8105,13 @@
         <v>26</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H150" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8119,7 +8119,7 @@
         <v>331</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C151" s="19" t="s">
         <v>332</v>
@@ -8131,13 +8131,13 @@
         <v>26</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H151" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8157,10 +8157,10 @@
         <v>26</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H152" s="15" t="s">
         <v>13</v>
@@ -8183,10 +8183,10 @@
         <v>26</v>
       </c>
       <c r="F153" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>13</v>
@@ -8209,10 +8209,10 @@
         <v>26</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>13</v>
@@ -8235,10 +8235,10 @@
         <v>26</v>
       </c>
       <c r="F155" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H155" s="20" t="s">
         <v>13</v>
@@ -8261,10 +8261,10 @@
         <v>26</v>
       </c>
       <c r="F156" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H156" s="15" t="s">
         <v>13</v>
@@ -8287,10 +8287,10 @@
         <v>26</v>
       </c>
       <c r="F157" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>13</v>
@@ -8313,10 +8313,10 @@
         <v>26</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H158" s="15" t="s">
         <v>13</v>
@@ -8339,10 +8339,10 @@
         <v>26</v>
       </c>
       <c r="F159" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>13</v>
@@ -8365,10 +8365,10 @@
         <v>26</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H160" s="15" t="s">
         <v>13</v>
@@ -8391,10 +8391,10 @@
         <v>26</v>
       </c>
       <c r="F161" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H161" s="20" t="s">
         <v>13</v>
@@ -8417,10 +8417,10 @@
         <v>26</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>13</v>
@@ -8443,10 +8443,10 @@
         <v>26</v>
       </c>
       <c r="F163" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H163" s="20" t="s">
         <v>13</v>
@@ -8469,10 +8469,10 @@
         <v>26</v>
       </c>
       <c r="F164" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H164" s="15" t="s">
         <v>13</v>
@@ -8495,10 +8495,10 @@
         <v>26</v>
       </c>
       <c r="F165" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H165" s="20" t="s">
         <v>13</v>
@@ -8521,10 +8521,10 @@
         <v>26</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H166" s="15" t="s">
         <v>13</v>
@@ -8547,10 +8547,10 @@
         <v>26</v>
       </c>
       <c r="F167" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G167" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H167" s="20" t="s">
         <v>13</v>
@@ -8573,10 +8573,10 @@
         <v>26</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H168" s="15" t="s">
         <v>13</v>
@@ -8599,10 +8599,10 @@
         <v>26</v>
       </c>
       <c r="F169" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H169" s="20" t="s">
         <v>13</v>
@@ -8625,10 +8625,10 @@
         <v>26</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H170" s="15" t="s">
         <v>13</v>
@@ -8651,10 +8651,10 @@
         <v>26</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G171" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H171" s="20" t="s">
         <v>13</v>
@@ -8677,10 +8677,10 @@
         <v>26</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H172" s="15" t="s">
         <v>13</v>
@@ -8703,10 +8703,10 @@
         <v>26</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G173" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H173" s="20" t="s">
         <v>13</v>
@@ -8729,10 +8729,10 @@
         <v>26</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H174" s="15" t="s">
         <v>13</v>
@@ -8755,10 +8755,10 @@
         <v>26</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G175" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H175" s="20" t="s">
         <v>13</v>
@@ -8781,10 +8781,10 @@
         <v>26</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H176" s="15" t="s">
         <v>13</v>
@@ -8807,10 +8807,10 @@
         <v>26</v>
       </c>
       <c r="F177" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G177" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H177" s="20" t="s">
         <v>13</v>
@@ -8833,10 +8833,10 @@
         <v>26</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H178" s="15" t="s">
         <v>13</v>
@@ -8859,10 +8859,10 @@
         <v>26</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G179" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H179" s="20" t="s">
         <v>13</v>
@@ -8885,13 +8885,13 @@
         <v>26</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H180" s="15" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8911,10 +8911,10 @@
         <v>26</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H181" s="20" t="s">
         <v>13</v>
@@ -8937,10 +8937,10 @@
         <v>26</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H182" s="15" t="s">
         <v>13</v>
@@ -8963,10 +8963,10 @@
         <v>26</v>
       </c>
       <c r="F183" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H183" s="20" t="s">
         <v>13</v>
@@ -8989,10 +8989,10 @@
         <v>26</v>
       </c>
       <c r="F184" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H184" s="15" t="s">
         <v>13</v>
@@ -9015,10 +9015,10 @@
         <v>26</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H185" s="20" t="s">
         <v>13</v>
@@ -9041,10 +9041,10 @@
         <v>26</v>
       </c>
       <c r="F186" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H186" s="15" t="s">
         <v>13</v>
@@ -9067,10 +9067,10 @@
         <v>26</v>
       </c>
       <c r="F187" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H187" s="20" t="s">
         <v>13</v>
@@ -9093,10 +9093,10 @@
         <v>26</v>
       </c>
       <c r="F188" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H188" s="15" t="s">
         <v>13</v>
@@ -9119,10 +9119,10 @@
         <v>26</v>
       </c>
       <c r="F189" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H189" s="20" t="s">
         <v>13</v>
@@ -9145,10 +9145,10 @@
         <v>26</v>
       </c>
       <c r="F190" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H190" s="15" t="s">
         <v>13</v>
@@ -9171,10 +9171,10 @@
         <v>26</v>
       </c>
       <c r="F191" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H191" s="20" t="s">
         <v>13</v>
@@ -9197,10 +9197,10 @@
         <v>26</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H192" s="15" t="s">
         <v>13</v>
@@ -9223,10 +9223,10 @@
         <v>26</v>
       </c>
       <c r="F193" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H193" s="20" t="s">
         <v>13</v>
@@ -9249,10 +9249,10 @@
         <v>26</v>
       </c>
       <c r="F194" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H194" s="15" t="s">
         <v>13</v>
@@ -9275,10 +9275,10 @@
         <v>26</v>
       </c>
       <c r="F195" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H195" s="20" t="s">
         <v>13</v>
@@ -9301,10 +9301,10 @@
         <v>26</v>
       </c>
       <c r="F196" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H196" s="15" t="s">
         <v>13</v>
@@ -9327,10 +9327,10 @@
         <v>26</v>
       </c>
       <c r="F197" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H197" s="20" t="s">
         <v>13</v>
@@ -9353,10 +9353,10 @@
         <v>26</v>
       </c>
       <c r="F198" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>13</v>
@@ -9379,10 +9379,10 @@
         <v>26</v>
       </c>
       <c r="F199" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H199" s="20" t="s">
         <v>13</v>
@@ -9405,10 +9405,10 @@
         <v>26</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H200" s="15" t="s">
         <v>13</v>
@@ -9431,10 +9431,10 @@
         <v>26</v>
       </c>
       <c r="F201" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G201" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H201" s="20" t="s">
         <v>13</v>
@@ -9457,10 +9457,10 @@
         <v>26</v>
       </c>
       <c r="F202" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>13</v>
@@ -9483,10 +9483,10 @@
         <v>26</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H203" s="20" t="s">
         <v>13</v>
@@ -9509,10 +9509,10 @@
         <v>26</v>
       </c>
       <c r="F204" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H204" s="15" t="s">
         <v>13</v>
@@ -9535,10 +9535,10 @@
         <v>26</v>
       </c>
       <c r="F205" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G205" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H205" s="20" t="s">
         <v>13</v>
@@ -9561,10 +9561,10 @@
         <v>26</v>
       </c>
       <c r="F206" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G206" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H206" s="15" t="s">
         <v>13</v>
@@ -9587,10 +9587,10 @@
         <v>26</v>
       </c>
       <c r="F207" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G207" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H207" s="20" t="s">
         <v>13</v>
@@ -9613,10 +9613,10 @@
         <v>26</v>
       </c>
       <c r="F208" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G208" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H208" s="15" t="s">
         <v>13</v>
@@ -9639,10 +9639,10 @@
         <v>26</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H209" s="20" t="s">
         <v>13</v>
@@ -9665,10 +9665,10 @@
         <v>26</v>
       </c>
       <c r="F210" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>13</v>
@@ -9691,10 +9691,10 @@
         <v>26</v>
       </c>
       <c r="F211" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G211" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H211" s="20" t="s">
         <v>13</v>
@@ -9717,10 +9717,10 @@
         <v>26</v>
       </c>
       <c r="F212" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H212" s="15" t="s">
         <v>13</v>
@@ -9743,10 +9743,10 @@
         <v>26</v>
       </c>
       <c r="F213" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H213" s="20" t="s">
         <v>13</v>
@@ -9769,10 +9769,10 @@
         <v>26</v>
       </c>
       <c r="F214" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G214" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H214" s="15" t="s">
         <v>13</v>
@@ -9795,10 +9795,10 @@
         <v>26</v>
       </c>
       <c r="F215" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H215" s="20" t="s">
         <v>13</v>
@@ -9821,10 +9821,10 @@
         <v>26</v>
       </c>
       <c r="F216" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G216" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H216" s="15" t="s">
         <v>13</v>
@@ -9847,10 +9847,10 @@
         <v>26</v>
       </c>
       <c r="F217" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H217" s="20" t="s">
         <v>13</v>
@@ -9873,10 +9873,10 @@
         <v>26</v>
       </c>
       <c r="F218" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H218" s="15" t="s">
         <v>13</v>
@@ -9899,10 +9899,10 @@
         <v>26</v>
       </c>
       <c r="F219" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H219" s="20" t="s">
         <v>13</v>
@@ -9925,10 +9925,10 @@
         <v>26</v>
       </c>
       <c r="F220" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H220" s="15" t="s">
         <v>13</v>
@@ -9951,10 +9951,10 @@
         <v>26</v>
       </c>
       <c r="F221" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H221" s="20" t="s">
         <v>13</v>
@@ -9977,10 +9977,10 @@
         <v>26</v>
       </c>
       <c r="F222" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>13</v>
@@ -10003,10 +10003,10 @@
         <v>26</v>
       </c>
       <c r="F223" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G223" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H223" s="20" t="s">
         <v>13</v>
@@ -10029,10 +10029,10 @@
         <v>26</v>
       </c>
       <c r="F224" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G224" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H224" s="15" t="s">
         <v>13</v>
@@ -10055,10 +10055,10 @@
         <v>26</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H225" s="20" t="s">
         <v>13</v>
@@ -10081,10 +10081,10 @@
         <v>26</v>
       </c>
       <c r="F226" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G226" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H226" s="15" t="s">
         <v>13</v>
@@ -10107,10 +10107,10 @@
         <v>26</v>
       </c>
       <c r="F227" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H227" s="20" t="s">
         <v>13</v>
@@ -10133,10 +10133,10 @@
         <v>26</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G228" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H228" s="15" t="s">
         <v>13</v>
@@ -10159,10 +10159,10 @@
         <v>26</v>
       </c>
       <c r="F229" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G229" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H229" s="20" t="s">
         <v>13</v>
@@ -10185,10 +10185,10 @@
         <v>26</v>
       </c>
       <c r="F230" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G230" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H230" s="15" t="s">
         <v>13</v>
@@ -10211,10 +10211,10 @@
         <v>26</v>
       </c>
       <c r="F231" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G231" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H231" s="20" t="s">
         <v>13</v>
@@ -10237,10 +10237,10 @@
         <v>26</v>
       </c>
       <c r="F232" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H232" s="15" t="s">
         <v>13</v>
@@ -10263,10 +10263,10 @@
         <v>26</v>
       </c>
       <c r="F233" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G233" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H233" s="20" t="s">
         <v>13</v>
@@ -10289,10 +10289,10 @@
         <v>26</v>
       </c>
       <c r="F234" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H234" s="15" t="s">
         <v>13</v>
@@ -10315,10 +10315,10 @@
         <v>26</v>
       </c>
       <c r="F235" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G235" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H235" s="20" t="s">
         <v>13</v>
@@ -10341,10 +10341,10 @@
         <v>26</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G236" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H236" s="15" t="s">
         <v>13</v>
@@ -10367,10 +10367,10 @@
         <v>26</v>
       </c>
       <c r="F237" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G237" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H237" s="20" t="s">
         <v>13</v>
@@ -10393,10 +10393,10 @@
         <v>26</v>
       </c>
       <c r="F238" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G238" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H238" s="15" t="s">
         <v>13</v>
@@ -10419,10 +10419,10 @@
         <v>26</v>
       </c>
       <c r="F239" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G239" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H239" s="20" t="s">
         <v>13</v>
@@ -10445,10 +10445,10 @@
         <v>26</v>
       </c>
       <c r="F240" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G240" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H240" s="15" t="s">
         <v>13</v>
@@ -10471,10 +10471,10 @@
         <v>26</v>
       </c>
       <c r="F241" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G241" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H241" s="20" t="s">
         <v>13</v>
@@ -10497,10 +10497,10 @@
         <v>26</v>
       </c>
       <c r="F242" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G242" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H242" s="15" t="s">
         <v>13</v>
@@ -10523,10 +10523,10 @@
         <v>26</v>
       </c>
       <c r="F243" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G243" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H243" s="20" t="s">
         <v>13</v>
@@ -10549,10 +10549,10 @@
         <v>26</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G244" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H244" s="15" t="s">
         <v>13</v>
@@ -10575,10 +10575,10 @@
         <v>26</v>
       </c>
       <c r="F245" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G245" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H245" s="20" t="s">
         <v>13</v>
@@ -10601,10 +10601,10 @@
         <v>26</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G246" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H246" s="15" t="s">
         <v>13</v>
@@ -10627,10 +10627,10 @@
         <v>26</v>
       </c>
       <c r="F247" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G247" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H247" s="20" t="s">
         <v>13</v>
@@ -10653,10 +10653,10 @@
         <v>26</v>
       </c>
       <c r="F248" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G248" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H248" s="15" t="s">
         <v>13</v>
@@ -10679,10 +10679,10 @@
         <v>26</v>
       </c>
       <c r="F249" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G249" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H249" s="20" t="s">
         <v>13</v>
@@ -10705,10 +10705,10 @@
         <v>26</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G250" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H250" s="15" t="s">
         <v>13</v>
@@ -10731,10 +10731,10 @@
         <v>26</v>
       </c>
       <c r="F251" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G251" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H251" s="20" t="s">
         <v>13</v>
@@ -10757,10 +10757,10 @@
         <v>26</v>
       </c>
       <c r="F252" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G252" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H252" s="15" t="s">
         <v>13</v>
@@ -10783,10 +10783,10 @@
         <v>26</v>
       </c>
       <c r="F253" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H253" s="20" t="s">
         <v>13</v>
@@ -10809,10 +10809,10 @@
         <v>26</v>
       </c>
       <c r="F254" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G254" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H254" s="15" t="s">
         <v>13</v>
@@ -10835,10 +10835,10 @@
         <v>26</v>
       </c>
       <c r="F255" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G255" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H255" s="20" t="s">
         <v>13</v>
@@ -10861,10 +10861,10 @@
         <v>26</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G256" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H256" s="15" t="s">
         <v>13</v>
@@ -10887,10 +10887,10 @@
         <v>26</v>
       </c>
       <c r="F257" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G257" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H257" s="20" t="s">
         <v>13</v>
@@ -10913,10 +10913,10 @@
         <v>26</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G258" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H258" s="15" t="s">
         <v>13</v>
@@ -10939,10 +10939,10 @@
         <v>26</v>
       </c>
       <c r="F259" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G259" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H259" s="20" t="s">
         <v>13</v>
@@ -10965,10 +10965,10 @@
         <v>26</v>
       </c>
       <c r="F260" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G260" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H260" s="15" t="s">
         <v>13</v>
@@ -10991,10 +10991,10 @@
         <v>26</v>
       </c>
       <c r="F261" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G261" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H261" s="20" t="s">
         <v>13</v>
@@ -11017,10 +11017,10 @@
         <v>26</v>
       </c>
       <c r="F262" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G262" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H262" s="15" t="s">
         <v>13</v>
@@ -11043,10 +11043,10 @@
         <v>26</v>
       </c>
       <c r="F263" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G263" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H263" s="20" t="s">
         <v>13</v>
@@ -11069,10 +11069,10 @@
         <v>26</v>
       </c>
       <c r="F264" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G264" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H264" s="15" t="s">
         <v>13</v>
@@ -11095,10 +11095,10 @@
         <v>26</v>
       </c>
       <c r="F265" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G265" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H265" s="20" t="s">
         <v>13</v>
@@ -11121,10 +11121,10 @@
         <v>26</v>
       </c>
       <c r="F266" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G266" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H266" s="15" t="s">
         <v>13</v>
@@ -11147,10 +11147,10 @@
         <v>26</v>
       </c>
       <c r="F267" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G267" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H267" s="20" t="s">
         <v>13</v>
@@ -11173,10 +11173,10 @@
         <v>26</v>
       </c>
       <c r="F268" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G268" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H268" s="15" t="s">
         <v>13</v>
@@ -11199,10 +11199,10 @@
         <v>26</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G269" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H269" s="20" t="s">
         <v>13</v>
@@ -11225,10 +11225,10 @@
         <v>26</v>
       </c>
       <c r="F270" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G270" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H270" s="15" t="s">
         <v>13</v>
@@ -11251,10 +11251,10 @@
         <v>26</v>
       </c>
       <c r="F271" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G271" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H271" s="20" t="s">
         <v>13</v>
@@ -11277,10 +11277,10 @@
         <v>26</v>
       </c>
       <c r="F272" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G272" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H272" s="15" t="s">
         <v>13</v>
@@ -11303,10 +11303,10 @@
         <v>26</v>
       </c>
       <c r="F273" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G273" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H273" s="20" t="s">
         <v>13</v>
@@ -11329,10 +11329,10 @@
         <v>26</v>
       </c>
       <c r="F274" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G274" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H274" s="15" t="s">
         <v>13</v>
@@ -11355,10 +11355,10 @@
         <v>26</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G275" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H275" s="20" t="s">
         <v>13</v>
@@ -11381,10 +11381,10 @@
         <v>26</v>
       </c>
       <c r="F276" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G276" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H276" s="15" t="s">
         <v>13</v>
@@ -11407,10 +11407,10 @@
         <v>26</v>
       </c>
       <c r="F277" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G277" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H277" s="20" t="s">
         <v>13</v>
@@ -11433,10 +11433,10 @@
         <v>26</v>
       </c>
       <c r="F278" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G278" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H278" s="15" t="s">
         <v>13</v>
@@ -11459,10 +11459,10 @@
         <v>26</v>
       </c>
       <c r="F279" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G279" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H279" s="20" t="s">
         <v>13</v>
@@ -11485,10 +11485,10 @@
         <v>26</v>
       </c>
       <c r="F280" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G280" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H280" s="15" t="s">
         <v>13</v>
@@ -11511,10 +11511,10 @@
         <v>26</v>
       </c>
       <c r="F281" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G281" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H281" s="20" t="s">
         <v>13</v>
@@ -11537,10 +11537,10 @@
         <v>26</v>
       </c>
       <c r="F282" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G282" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H282" s="15" t="s">
         <v>13</v>
@@ -11563,10 +11563,10 @@
         <v>26</v>
       </c>
       <c r="F283" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G283" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H283" s="20" t="s">
         <v>13</v>
@@ -11589,10 +11589,10 @@
         <v>26</v>
       </c>
       <c r="F284" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G284" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H284" s="15" t="s">
         <v>13</v>
@@ -11615,10 +11615,10 @@
         <v>26</v>
       </c>
       <c r="F285" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G285" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H285" s="20" t="s">
         <v>13</v>
@@ -11641,10 +11641,10 @@
         <v>26</v>
       </c>
       <c r="F286" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G286" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H286" s="15" t="s">
         <v>13</v>
@@ -11667,10 +11667,10 @@
         <v>26</v>
       </c>
       <c r="F287" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G287" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H287" s="20" t="s">
         <v>13</v>
@@ -11693,10 +11693,10 @@
         <v>26</v>
       </c>
       <c r="F288" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G288" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H288" s="15" t="s">
         <v>13</v>
@@ -11719,10 +11719,10 @@
         <v>26</v>
       </c>
       <c r="F289" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G289" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H289" s="20" t="s">
         <v>13</v>
@@ -11745,10 +11745,10 @@
         <v>26</v>
       </c>
       <c r="F290" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G290" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H290" s="15" t="s">
         <v>13</v>
@@ -11771,10 +11771,10 @@
         <v>26</v>
       </c>
       <c r="F291" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G291" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H291" s="20" t="s">
         <v>13</v>
@@ -11797,10 +11797,10 @@
         <v>26</v>
       </c>
       <c r="F292" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G292" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H292" s="15" t="s">
         <v>13</v>
@@ -11823,10 +11823,10 @@
         <v>26</v>
       </c>
       <c r="F293" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G293" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H293" s="20" t="s">
         <v>13</v>
@@ -11849,10 +11849,10 @@
         <v>26</v>
       </c>
       <c r="F294" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G294" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H294" s="15" t="s">
         <v>13</v>
@@ -11875,10 +11875,10 @@
         <v>26</v>
       </c>
       <c r="F295" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G295" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H295" s="20" t="s">
         <v>13</v>
@@ -11901,10 +11901,10 @@
         <v>26</v>
       </c>
       <c r="F296" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G296" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H296" s="15" t="s">
         <v>13</v>
@@ -11927,10 +11927,10 @@
         <v>26</v>
       </c>
       <c r="F297" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G297" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H297" s="20" t="s">
         <v>13</v>
@@ -11953,10 +11953,10 @@
         <v>26</v>
       </c>
       <c r="F298" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G298" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H298" s="15" t="s">
         <v>13</v>
@@ -11979,10 +11979,10 @@
         <v>26</v>
       </c>
       <c r="F299" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G299" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H299" s="20" t="s">
         <v>13</v>
@@ -12005,10 +12005,10 @@
         <v>26</v>
       </c>
       <c r="F300" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G300" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H300" s="15" t="s">
         <v>13</v>
@@ -12031,10 +12031,10 @@
         <v>26</v>
       </c>
       <c r="F301" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G301" s="20" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="H301" s="20" t="s">
         <v>13</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B80" s="24" t="s">
         <v>807</v>
@@ -13472,7 +13472,7 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>809</v>
@@ -13489,7 +13489,7 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B82" s="24" t="s">
         <v>811</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>813</v>
@@ -13523,7 +13523,7 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="24" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B84" s="24" t="s">
         <v>815</v>
@@ -13540,7 +13540,7 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>817</v>
@@ -13557,7 +13557,7 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B86" s="24" t="s">
         <v>819</v>
@@ -13574,7 +13574,7 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>821</v>
@@ -13591,7 +13591,7 @@
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B88" s="24" t="s">
         <v>823</v>
@@ -13608,7 +13608,7 @@
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>825</v>
@@ -13625,7 +13625,7 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B90" s="24" t="s">
         <v>827</v>
@@ -13642,7 +13642,7 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>829</v>
@@ -13659,7 +13659,7 @@
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B92" s="24" t="s">
         <v>831</v>
@@ -13676,7 +13676,7 @@
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>833</v>
@@ -13693,7 +13693,7 @@
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B94" s="24" t="s">
         <v>835</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>837</v>
@@ -13727,7 +13727,7 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B96" s="24" t="s">
         <v>839</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>841</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B98" s="24" t="s">
         <v>843</v>
@@ -13778,7 +13778,7 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>845</v>
@@ -13795,7 +13795,7 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B100" s="24" t="s">
         <v>847</v>
@@ -13812,7 +13812,7 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>849</v>
@@ -13829,7 +13829,7 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B102" s="24" t="s">
         <v>851</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>854</v>
@@ -13863,7 +13863,7 @@
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B104" s="24" t="s">
         <v>856</v>
@@ -13880,7 +13880,7 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>858</v>
@@ -13897,7 +13897,7 @@
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B106" s="24" t="s">
         <v>860</v>
@@ -13914,7 +13914,7 @@
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>862</v>
@@ -13931,7 +13931,7 @@
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B108" s="24" t="s">
         <v>864</v>
@@ -13948,7 +13948,7 @@
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>866</v>
@@ -13965,7 +13965,7 @@
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B110" s="24" t="s">
         <v>868</v>
@@ -13982,7 +13982,7 @@
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>870</v>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B112" s="24" t="s">
         <v>872</v>
@@ -14016,7 +14016,7 @@
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>874</v>
@@ -14033,7 +14033,7 @@
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B114" s="24" t="s">
         <v>876</v>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B115" s="26" t="s">
         <v>878</v>
@@ -14067,7 +14067,7 @@
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B116" s="24" t="s">
         <v>880</v>
@@ -14084,7 +14084,7 @@
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>882</v>
@@ -14101,7 +14101,7 @@
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B118" s="24" t="s">
         <v>884</v>
@@ -14118,7 +14118,7 @@
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>886</v>
@@ -14135,7 +14135,7 @@
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="24" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B120" s="24" t="s">
         <v>888</v>
@@ -14152,7 +14152,7 @@
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B121" s="26" t="s">
         <v>890</v>
@@ -14169,7 +14169,7 @@
     </row>
     <row r="122" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B122" s="24" t="s">
         <v>892</v>
@@ -14186,7 +14186,7 @@
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B123" s="26" t="s">
         <v>894</v>
@@ -14203,7 +14203,7 @@
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B124" s="24" t="s">
         <v>896</v>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B125" s="26" t="s">
         <v>898</v>
@@ -14237,7 +14237,7 @@
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B126" s="24" t="s">
         <v>900</v>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>902</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B128" s="24" t="s">
         <v>904</v>
@@ -14288,7 +14288,7 @@
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>906</v>
@@ -14305,7 +14305,7 @@
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B130" s="24" t="s">
         <v>908</v>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B131" s="26" t="s">
         <v>910</v>
@@ -14339,7 +14339,7 @@
     </row>
     <row r="132" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B132" s="24" t="s">
         <v>912</v>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="133" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B133" s="26" t="s">
         <v>914</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="134" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>916</v>
@@ -14390,7 +14390,7 @@
     </row>
     <row r="135" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B135" s="26" t="s">
         <v>918</v>
@@ -14407,7 +14407,7 @@
     </row>
     <row r="136" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>920</v>
@@ -14424,7 +14424,7 @@
     </row>
     <row r="137" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B137" s="26" t="s">
         <v>922</v>
@@ -14441,7 +14441,7 @@
     </row>
     <row r="138" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B138" s="24" t="s">
         <v>924</v>
@@ -14458,7 +14458,7 @@
     </row>
     <row r="139" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B139" s="26" t="s">
         <v>926</v>
@@ -14475,7 +14475,7 @@
     </row>
     <row r="140" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B140" s="24" t="s">
         <v>928</v>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="141" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B141" s="26" t="s">
         <v>930</v>
@@ -14509,7 +14509,7 @@
     </row>
     <row r="142" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B142" s="24" t="s">
         <v>932</v>
@@ -14526,7 +14526,7 @@
     </row>
     <row r="143" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B143" s="26" t="s">
         <v>934</v>
@@ -14543,7 +14543,7 @@
     </row>
     <row r="144" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B144" s="24" t="s">
         <v>936</v>
@@ -14560,7 +14560,7 @@
     </row>
     <row r="145" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B145" s="26" t="s">
         <v>938</v>
@@ -14577,7 +14577,7 @@
     </row>
     <row r="146" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B146" s="24" t="s">
         <v>940</v>
@@ -14594,7 +14594,7 @@
     </row>
     <row r="147" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B147" s="26" t="s">
         <v>942</v>
@@ -14611,7 +14611,7 @@
     </row>
     <row r="148" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B148" s="24" t="s">
         <v>944</v>
@@ -14628,7 +14628,7 @@
     </row>
     <row r="149" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B149" s="26" t="s">
         <v>946</v>
@@ -14645,7 +14645,7 @@
     </row>
     <row r="150" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B150" s="24" t="s">
         <v>948</v>
@@ -14662,7 +14662,7 @@
     </row>
     <row r="151" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B151" s="26" t="s">
         <v>950</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="152" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B152" s="24" t="s">
         <v>952</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="153" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B153" s="26" t="s">
         <v>955</v>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="154" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B154" s="24" t="s">
         <v>957</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="155" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B155" s="26" t="s">
         <v>959</v>
@@ -14747,7 +14747,7 @@
     </row>
     <row r="156" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B156" s="24" t="s">
         <v>961</v>
@@ -14764,7 +14764,7 @@
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B157" s="26" t="s">
         <v>963</v>
@@ -14781,7 +14781,7 @@
     </row>
     <row r="158" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B158" s="24" t="s">
         <v>965</v>
@@ -14798,7 +14798,7 @@
     </row>
     <row r="159" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B159" s="26" t="s">
         <v>967</v>
@@ -14815,7 +14815,7 @@
     </row>
     <row r="160" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B160" s="24" t="s">
         <v>969</v>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="161" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B161" s="26" t="s">
         <v>971</v>
@@ -14849,7 +14849,7 @@
     </row>
     <row r="162" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B162" s="24" t="s">
         <v>973</v>
@@ -14866,7 +14866,7 @@
     </row>
     <row r="163" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B163" s="26" t="s">
         <v>975</v>
@@ -14883,7 +14883,7 @@
     </row>
     <row r="164" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B164" s="24" t="s">
         <v>977</v>
@@ -14900,7 +14900,7 @@
     </row>
     <row r="165" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B165" s="26" t="s">
         <v>979</v>
@@ -14917,7 +14917,7 @@
     </row>
     <row r="166" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B166" s="24" t="s">
         <v>981</v>
@@ -14934,7 +14934,7 @@
     </row>
     <row r="167" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B167" s="26" t="s">
         <v>983</v>
@@ -14951,7 +14951,7 @@
     </row>
     <row r="168" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B168" s="24" t="s">
         <v>985</v>
@@ -14968,7 +14968,7 @@
     </row>
     <row r="169" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B169" s="26" t="s">
         <v>987</v>
@@ -14985,7 +14985,7 @@
     </row>
     <row r="170" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B170" s="24" t="s">
         <v>989</v>
@@ -15002,7 +15002,7 @@
     </row>
     <row r="171" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B171" s="26" t="s">
         <v>991</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="172" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B172" s="24" t="s">
         <v>993</v>
@@ -15036,7 +15036,7 @@
     </row>
     <row r="173" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B173" s="26" t="s">
         <v>995</v>
@@ -15053,7 +15053,7 @@
     </row>
     <row r="174" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B174" s="24" t="s">
         <v>997</v>
@@ -15070,7 +15070,7 @@
     </row>
     <row r="175" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B175" s="26" t="s">
         <v>999</v>
@@ -15087,7 +15087,7 @@
     </row>
     <row r="176" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B176" s="24" t="s">
         <v>1001</v>
@@ -15104,7 +15104,7 @@
     </row>
     <row r="177" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B177" s="26" t="s">
         <v>1003</v>
@@ -15121,7 +15121,7 @@
     </row>
     <row r="178" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B178" s="24" t="s">
         <v>1005</v>
@@ -15138,7 +15138,7 @@
     </row>
     <row r="179" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B179" s="26" t="s">
         <v>1007</v>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="180" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B180" s="24" t="s">
         <v>1009</v>
@@ -15172,7 +15172,7 @@
     </row>
     <row r="181" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B181" s="26" t="s">
         <v>1011</v>
@@ -15189,7 +15189,7 @@
     </row>
     <row r="182" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B182" s="24" t="s">
         <v>1013</v>
@@ -15206,7 +15206,7 @@
     </row>
     <row r="183" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B183" s="26" t="s">
         <v>1015</v>
@@ -15223,7 +15223,7 @@
     </row>
     <row r="184" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B184" s="24" t="s">
         <v>1017</v>
@@ -15240,7 +15240,7 @@
     </row>
     <row r="185" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B185" s="26" t="s">
         <v>1019</v>
@@ -15257,7 +15257,7 @@
     </row>
     <row r="186" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B186" s="24" t="s">
         <v>1021</v>
@@ -15274,7 +15274,7 @@
     </row>
     <row r="187" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B187" s="26" t="s">
         <v>1023</v>
@@ -15291,7 +15291,7 @@
     </row>
     <row r="188" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B188" s="24" t="s">
         <v>1025</v>
@@ -15308,7 +15308,7 @@
     </row>
     <row r="189" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B189" s="26" t="s">
         <v>1027</v>
@@ -15325,7 +15325,7 @@
     </row>
     <row r="190" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B190" s="24" t="s">
         <v>1029</v>
@@ -15342,7 +15342,7 @@
     </row>
     <row r="191" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B191" s="26" t="s">
         <v>1031</v>
@@ -15359,7 +15359,7 @@
     </row>
     <row r="192" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B192" s="24" t="s">
         <v>1033</v>
@@ -15376,7 +15376,7 @@
     </row>
     <row r="193" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B193" s="26" t="s">
         <v>1035</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="194" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B194" s="24" t="s">
         <v>1037</v>
@@ -15410,7 +15410,7 @@
     </row>
     <row r="195" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B195" s="26" t="s">
         <v>1039</v>
@@ -15427,7 +15427,7 @@
     </row>
     <row r="196" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B196" s="24" t="s">
         <v>1041</v>
@@ -15444,7 +15444,7 @@
     </row>
     <row r="197" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B197" s="26" t="s">
         <v>1043</v>
@@ -15461,7 +15461,7 @@
     </row>
     <row r="198" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B198" s="24" t="s">
         <v>1045</v>
@@ -15478,7 +15478,7 @@
     </row>
     <row r="199" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B199" s="26" t="s">
         <v>1047</v>
@@ -15495,7 +15495,7 @@
     </row>
     <row r="200" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B200" s="24" t="s">
         <v>1049</v>
@@ -15512,7 +15512,7 @@
     </row>
     <row r="201" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B201" s="26" t="s">
         <v>1051</v>
@@ -15529,7 +15529,7 @@
     </row>
     <row r="202" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B202" s="24" t="s">
         <v>1053</v>
@@ -15546,7 +15546,7 @@
     </row>
     <row r="203" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B203" s="26" t="s">
         <v>1056</v>
@@ -15563,7 +15563,7 @@
     </row>
     <row r="204" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B204" s="24" t="s">
         <v>1058</v>
@@ -15580,7 +15580,7 @@
     </row>
     <row r="205" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B205" s="26" t="s">
         <v>1060</v>
@@ -15597,7 +15597,7 @@
     </row>
     <row r="206" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B206" s="24" t="s">
         <v>1062</v>
@@ -15614,7 +15614,7 @@
     </row>
     <row r="207" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B207" s="26" t="s">
         <v>1064</v>
@@ -15631,7 +15631,7 @@
     </row>
     <row r="208" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B208" s="24" t="s">
         <v>1066</v>
@@ -15648,7 +15648,7 @@
     </row>
     <row r="209" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B209" s="26" t="s">
         <v>1068</v>
@@ -15665,7 +15665,7 @@
     </row>
     <row r="210" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B210" s="24" t="s">
         <v>1070</v>
@@ -15682,7 +15682,7 @@
     </row>
     <row r="211" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B211" s="26" t="s">
         <v>1072</v>
@@ -15699,7 +15699,7 @@
     </row>
     <row r="212" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B212" s="24" t="s">
         <v>1074</v>
@@ -15716,7 +15716,7 @@
     </row>
     <row r="213" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B213" s="26" t="s">
         <v>1076</v>
@@ -15733,7 +15733,7 @@
     </row>
     <row r="214" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B214" s="24" t="s">
         <v>1078</v>
@@ -15750,7 +15750,7 @@
     </row>
     <row r="215" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B215" s="26" t="s">
         <v>1080</v>
@@ -15767,7 +15767,7 @@
     </row>
     <row r="216" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B216" s="24" t="s">
         <v>1082</v>
@@ -15784,7 +15784,7 @@
     </row>
     <row r="217" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B217" s="26" t="s">
         <v>1084</v>
@@ -15801,7 +15801,7 @@
     </row>
     <row r="218" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B218" s="24" t="s">
         <v>1086</v>
@@ -15818,7 +15818,7 @@
     </row>
     <row r="219" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B219" s="26" t="s">
         <v>1088</v>
@@ -15835,7 +15835,7 @@
     </row>
     <row r="220" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B220" s="24" t="s">
         <v>1090</v>
@@ -15852,7 +15852,7 @@
     </row>
     <row r="221" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B221" s="26" t="s">
         <v>1092</v>
@@ -15869,7 +15869,7 @@
     </row>
     <row r="222" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B222" s="24" t="s">
         <v>1094</v>
@@ -15886,7 +15886,7 @@
     </row>
     <row r="223" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B223" s="26" t="s">
         <v>1096</v>
@@ -15903,7 +15903,7 @@
     </row>
     <row r="224" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B224" s="24" t="s">
         <v>1098</v>
@@ -15920,7 +15920,7 @@
     </row>
     <row r="225" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B225" s="26" t="s">
         <v>1100</v>
@@ -15937,7 +15937,7 @@
     </row>
     <row r="226" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B226" s="24" t="s">
         <v>1102</v>
@@ -15954,7 +15954,7 @@
     </row>
     <row r="227" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B227" s="26" t="s">
         <v>1104</v>
@@ -15971,7 +15971,7 @@
     </row>
     <row r="228" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B228" s="24" t="s">
         <v>1106</v>
@@ -15988,7 +15988,7 @@
     </row>
     <row r="229" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B229" s="26" t="s">
         <v>1108</v>
@@ -16005,7 +16005,7 @@
     </row>
     <row r="230" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B230" s="24" t="s">
         <v>1110</v>
@@ -16022,7 +16022,7 @@
     </row>
     <row r="231" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B231" s="26" t="s">
         <v>1112</v>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="232" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B232" s="24" t="s">
         <v>1114</v>
@@ -16056,7 +16056,7 @@
     </row>
     <row r="233" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B233" s="26" t="s">
         <v>1116</v>
@@ -16073,7 +16073,7 @@
     </row>
     <row r="234" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B234" s="24" t="s">
         <v>1118</v>
@@ -16090,7 +16090,7 @@
     </row>
     <row r="235" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B235" s="26" t="s">
         <v>1120</v>
@@ -16107,7 +16107,7 @@
     </row>
     <row r="236" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B236" s="24" t="s">
         <v>1122</v>
@@ -16124,7 +16124,7 @@
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B237" s="26" t="s">
         <v>1124</v>
@@ -16141,7 +16141,7 @@
     </row>
     <row r="238" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B238" s="24" t="s">
         <v>1126</v>
@@ -16158,7 +16158,7 @@
     </row>
     <row r="239" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B239" s="26" t="s">
         <v>1128</v>
@@ -16175,7 +16175,7 @@
     </row>
     <row r="240" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B240" s="24" t="s">
         <v>1130</v>
@@ -16192,7 +16192,7 @@
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B241" s="26" t="s">
         <v>1132</v>
@@ -16209,7 +16209,7 @@
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B242" s="24" t="s">
         <v>1134</v>
@@ -16226,7 +16226,7 @@
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B243" s="26" t="s">
         <v>1136</v>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B244" s="24" t="s">
         <v>1138</v>
@@ -16260,7 +16260,7 @@
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B245" s="26" t="s">
         <v>1140</v>
@@ -16277,7 +16277,7 @@
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B246" s="24" t="s">
         <v>1142</v>
@@ -16294,7 +16294,7 @@
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B247" s="26" t="s">
         <v>1144</v>
@@ -16311,7 +16311,7 @@
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B248" s="24" t="s">
         <v>1146</v>
@@ -16328,7 +16328,7 @@
     </row>
     <row r="249" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B249" s="26" t="s">
         <v>1148</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="250" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="24" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B250" s="24" t="s">
         <v>1150</v>
@@ -16362,7 +16362,7 @@
     </row>
     <row r="251" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="26" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B251" s="26" t="s">
         <v>1152</v>

--- a/reports/excel/Load_Report.xlsx
+++ b/reports/excel/Load_Report.xlsx
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 04:41:24</t>
+    <t>2026-08-20 03:51:22</t>
   </si>
   <si>
     <t>TC-LOAD-002</t>
@@ -409,27 +409,27 @@
     <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 2/5)</t>
   </si>
   <si>
+    <t>TC-LOAD-053</t>
+  </si>
+  <si>
+    <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 3/5)</t>
+  </si>
+  <si>
+    <t>TC-LOAD-054</t>
+  </si>
+  <si>
+    <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 4/5)</t>
+  </si>
+  <si>
+    <t>TC-LOAD-055</t>
+  </si>
+  <si>
+    <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 5/5)</t>
+  </si>
+  <si>
     <t>0.01s</t>
   </si>
   <si>
-    <t>TC-LOAD-053</t>
-  </si>
-  <si>
-    <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 3/5)</t>
-  </si>
-  <si>
-    <t>TC-LOAD-054</t>
-  </si>
-  <si>
-    <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 4/5)</t>
-  </si>
-  <si>
-    <t>TC-LOAD-055</t>
-  </si>
-  <si>
-    <t>Concurrency: 5 VU Concurrent Feed Requests (Batch Cycle 5/5)</t>
-  </si>
-  <si>
     <t>TC-LOAD-056</t>
   </si>
   <si>
@@ -496,15 +496,15 @@
     <t>Concurrency: 20 VU Concurrent Feed Requests (Batch Cycle 1/5)</t>
   </si>
   <si>
+    <t>0.02s</t>
+  </si>
+  <si>
     <t>TC-LOAD-067</t>
   </si>
   <si>
     <t>Concurrency: 20 VU Concurrent Feed Requests (Batch Cycle 2/5)</t>
   </si>
   <si>
-    <t>0.02s</t>
-  </si>
-  <si>
     <t>TC-LOAD-068</t>
   </si>
   <si>
@@ -571,12 +571,6 @@
     <t>Concurrency: 5 VU Concurrent /api/cluster Requests (Batch Cycle 3/5)</t>
   </si>
   <si>
-    <t>2026-08-20 04:41:25</t>
-  </si>
-  <si>
-    <t>0.76s</t>
-  </si>
-  <si>
     <t>TC-LOAD-079</t>
   </si>
   <si>
@@ -631,6 +625,9 @@
     <t>Concurrency: 15 VU Concurrent /api/regions Requests (Batch Cycle 2/5)</t>
   </si>
   <si>
+    <t>2026-08-20 03:51:23</t>
+  </si>
+  <si>
     <t>TC-LOAD-088</t>
   </si>
   <si>
@@ -808,12 +805,18 @@
     <t>Stress: Rapid traffic burst on Settings Page (Burst Round 1/5)</t>
   </si>
   <si>
+    <t>0.03s</t>
+  </si>
+  <si>
     <t>TC-LOAD-117</t>
   </si>
   <si>
     <t>Stress: Rapid traffic burst on Settings Page (Burst Round 2/5)</t>
   </si>
   <si>
+    <t>0.04s</t>
+  </si>
+  <si>
     <t>TC-LOAD-118</t>
   </si>
   <si>
@@ -824,9 +827,6 @@
   </si>
   <si>
     <t>Stress: Rapid traffic burst on Settings Page (Burst Round 4/5)</t>
-  </si>
-  <si>
-    <t>2026-08-20 04:41:26</t>
   </si>
   <si>
     <t>TC-LOAD-120</t>
@@ -5589,18 +5589,18 @@
         <v>27</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>25</v>
@@ -5620,13 +5620,13 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>25</v>
@@ -5646,28 +5646,28 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C56" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="15" t="s">
         <v>137</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G56" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>27</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5719,7 +5719,7 @@
         <v>27</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5745,7 +5745,7 @@
         <v>27</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5771,7 +5771,7 @@
         <v>27</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5797,7 +5797,7 @@
         <v>27</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5823,7 +5823,7 @@
         <v>27</v>
       </c>
       <c r="H62" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5875,7 +5875,7 @@
         <v>27</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5901,7 +5901,7 @@
         <v>27</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5927,7 +5927,7 @@
         <v>27</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5953,18 +5953,18 @@
         <v>27</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>25</v>
@@ -5979,7 +5979,7 @@
         <v>27</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6005,7 +6005,7 @@
         <v>27</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6031,7 +6031,7 @@
         <v>27</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6057,7 +6057,7 @@
         <v>27</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6083,7 +6083,7 @@
         <v>27</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6135,7 +6135,7 @@
         <v>27</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6161,7 +6161,7 @@
         <v>27</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
         <v>27</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6239,7 +6239,7 @@
         <v>27</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -6262,21 +6262,21 @@
         <v>27</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>25</v>
@@ -6285,10 +6285,10 @@
         <v>26</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H80" s="15" t="s">
         <v>13</v>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>25</v>
@@ -6311,10 +6311,10 @@
         <v>26</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H81" s="20" t="s">
         <v>13</v>
@@ -6322,13 +6322,13 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>25</v>
@@ -6337,10 +6337,10 @@
         <v>26</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H82" s="15" t="s">
         <v>13</v>
@@ -6348,13 +6348,13 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>25</v>
@@ -6363,24 +6363,24 @@
         <v>26</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B84" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>25</v>
@@ -6389,10 +6389,10 @@
         <v>26</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H84" s="15" t="s">
         <v>13</v>
@@ -6400,13 +6400,13 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B85" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>25</v>
@@ -6415,10 +6415,10 @@
         <v>26</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H85" s="20" t="s">
         <v>13</v>
@@ -6426,13 +6426,13 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B86" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>25</v>
@@ -6441,24 +6441,24 @@
         <v>26</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>25</v>
@@ -6467,24 +6467,24 @@
         <v>26</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B88" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>25</v>
@@ -6493,24 +6493,24 @@
         <v>26</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B89" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>25</v>
@@ -6519,24 +6519,24 @@
         <v>26</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B90" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>25</v>
@@ -6545,24 +6545,24 @@
         <v>26</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B91" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>25</v>
@@ -6571,24 +6571,24 @@
         <v>26</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B92" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>25</v>
@@ -6597,24 +6597,24 @@
         <v>26</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H92" s="15" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B93" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>25</v>
@@ -6623,24 +6623,24 @@
         <v>26</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>25</v>
@@ -6649,24 +6649,24 @@
         <v>26</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G94" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B95" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>25</v>
@@ -6675,24 +6675,24 @@
         <v>26</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H95" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B96" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>25</v>
@@ -6701,24 +6701,24 @@
         <v>26</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G96" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B97" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>25</v>
@@ -6727,24 +6727,24 @@
         <v>26</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B98" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>25</v>
@@ -6753,24 +6753,24 @@
         <v>26</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H98" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B99" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>25</v>
@@ -6779,24 +6779,24 @@
         <v>26</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B100" s="13" t="s">
         <v>127</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>25</v>
@@ -6805,24 +6805,24 @@
         <v>26</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B101" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>25</v>
@@ -6831,25 +6831,25 @@
         <v>26</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B102" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="C102" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C102" s="14" t="s">
-        <v>233</v>
-      </c>
       <c r="D102" s="15" t="s">
         <v>25</v>
       </c>
@@ -6857,25 +6857,25 @@
         <v>26</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C103" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="B103" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>235</v>
-      </c>
       <c r="D103" s="20" t="s">
         <v>25</v>
       </c>
@@ -6883,25 +6883,25 @@
         <v>26</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C104" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B104" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C104" s="14" t="s">
-        <v>237</v>
-      </c>
       <c r="D104" s="15" t="s">
         <v>25</v>
       </c>
@@ -6909,25 +6909,25 @@
         <v>26</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C105" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="B105" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>239</v>
-      </c>
       <c r="D105" s="20" t="s">
         <v>25</v>
       </c>
@@ -6935,25 +6935,25 @@
         <v>26</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C106" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="B106" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>241</v>
-      </c>
       <c r="D106" s="15" t="s">
         <v>25</v>
       </c>
@@ -6961,25 +6961,25 @@
         <v>26</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="B107" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>243</v>
-      </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
       </c>
@@ -6987,25 +6987,25 @@
         <v>26</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C108" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="B108" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>245</v>
-      </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
       </c>
@@ -7013,25 +7013,25 @@
         <v>26</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C109" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="B109" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>247</v>
-      </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
       </c>
@@ -7039,25 +7039,25 @@
         <v>26</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="B110" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>249</v>
-      </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
       </c>
@@ -7065,10 +7065,10 @@
         <v>26</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H110" s="15" t="s">
         <v>13</v>
@@ -7076,14 +7076,14 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="B111" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
       </c>
@@ -7091,10 +7091,10 @@
         <v>26</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H111" s="20" t="s">
         <v>13</v>
@@ -7102,14 +7102,14 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C112" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="B112" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
       </c>
@@ -7117,25 +7117,25 @@
         <v>26</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C113" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="B113" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>255</v>
-      </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
       </c>
@@ -7143,25 +7143,25 @@
         <v>26</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C114" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="B114" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
       </c>
@@ -7169,25 +7169,25 @@
         <v>26</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="B115" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>259</v>
-      </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
       </c>
@@ -7195,10 +7195,10 @@
         <v>26</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H115" s="20" t="s">
         <v>13</v>
@@ -7206,14 +7206,14 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C116" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="B116" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C116" s="14" t="s">
-        <v>261</v>
-      </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
       </c>
@@ -7221,39 +7221,39 @@
         <v>26</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C117" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C117" s="19" t="s">
+      <c r="D117" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E117" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G117" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H117" s="20" t="s">
         <v>263</v>
-      </c>
-      <c r="D117" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E117" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F117" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="G117" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H117" s="20" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7261,7 +7261,7 @@
         <v>264</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C118" s="14" t="s">
         <v>265</v>
@@ -7273,24 +7273,24 @@
         <v>26</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>131</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
@@ -7299,24 +7299,24 @@
         <v>26</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
@@ -7325,13 +7325,13 @@
         <v>26</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7339,7 +7339,7 @@
         <v>271</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C121" s="19" t="s">
         <v>272</v>
@@ -7351,13 +7351,13 @@
         <v>26</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7365,7 +7365,7 @@
         <v>273</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>274</v>
@@ -7377,13 +7377,13 @@
         <v>26</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H122" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7391,7 +7391,7 @@
         <v>275</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C123" s="19" t="s">
         <v>276</v>
@@ -7403,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7417,7 +7417,7 @@
         <v>277</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C124" s="14" t="s">
         <v>278</v>
@@ -7429,13 +7429,13 @@
         <v>26</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7443,7 +7443,7 @@
         <v>279</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C125" s="19" t="s">
         <v>280</v>
@@ -7455,13 +7455,13 @@
         <v>26</v>
       </c>
       <c r="F125" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H125" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7469,7 +7469,7 @@
         <v>281</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C126" s="14" t="s">
         <v>282</v>
@@ -7481,13 +7481,13 @@
         <v>26</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H126" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7495,7 +7495,7 @@
         <v>283</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C127" s="19" t="s">
         <v>284</v>
@@ -7507,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="F127" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H127" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7521,7 +7521,7 @@
         <v>285</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C128" s="14" t="s">
         <v>286</v>
@@ -7533,13 +7533,13 @@
         <v>26</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H128" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7547,7 +7547,7 @@
         <v>287</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C129" s="19" t="s">
         <v>288</v>
@@ -7559,13 +7559,13 @@
         <v>26</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H129" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>289</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>290</v>
@@ -7585,13 +7585,13 @@
         <v>26</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H130" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7599,7 +7599,7 @@
         <v>291</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C131" s="19" t="s">
         <v>292</v>
@@ -7611,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="F131" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G131" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H131" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7625,7 +7625,7 @@
         <v>293</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C132" s="14" t="s">
         <v>294</v>
@@ -7637,13 +7637,13 @@
         <v>26</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H132" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7651,7 +7651,7 @@
         <v>295</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C133" s="19" t="s">
         <v>296</v>
@@ -7663,13 +7663,13 @@
         <v>26</v>
       </c>
       <c r="F133" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H133" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>297</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>298</v>
@@ -7689,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7703,7 +7703,7 @@
         <v>299</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C135" s="19" t="s">
         <v>300</v>
@@ -7715,13 +7715,13 @@
         <v>26</v>
       </c>
       <c r="F135" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H135" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7729,7 +7729,7 @@
         <v>301</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C136" s="14" t="s">
         <v>302</v>
@@ -7741,13 +7741,13 @@
         <v>26</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H136" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7755,7 +7755,7 @@
         <v>303</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C137" s="19" t="s">
         <v>304</v>
@@ -7767,13 +7767,13 @@
         <v>26</v>
       </c>
       <c r="F137" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H137" s="20" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>305</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C138" s="14" t="s">
         <v>306</v>
@@ -7793,13 +7793,13 @@
         <v>26</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H138" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7807,7 +7807,7 @@
         <v>307</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C139" s="19" t="s">
         <v>308</v>
@@ -7819,13 +7819,13 @@
         <v>26</v>
       </c>
       <c r="F139" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H139" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
         <v>309</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>310</v>
@@ -7845,13 +7845,13 @@
         <v>26</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7859,7 +7859,7 @@
         <v>311</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C141" s="19" t="s">
         <v>312</v>
@@ -7871,13 +7871,13 @@
         <v>26</v>
       </c>
       <c r="F141" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H141" s="20" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7885,7 +7885,7 @@
         <v>313</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C142" s="14" t="s">
         <v>314</v>
@@ -7897,10 +7897,10 @@
         <v>26</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H142" s="15" t="s">
         <v>13</v>
@@ -7911,7 +7911,7 @@
         <v>315</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C143" s="19" t="s">
         <v>316</v>
@@ -7923,13 +7923,13 @@
         <v>26</v>
       </c>
       <c r="F143" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H143" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7937,7 +7937,7 @@
         <v>317</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>318</v>
@@ -7949,13 +7949,13 @@
         <v>26</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7963,7 +7963,7 @@
         <v>319</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C145" s="19" t="s">
         <v>320</v>
@@ -7975,13 +7975,13 @@
         <v>26</v>
       </c>
       <c r="F145" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H145" s="20" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -7989,7 +7989,7 @@
         <v>321</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>322</v>
@@ -8001,13 +8001,13 @@
         <v>26</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8015,7 +8015,7 @@
         <v>323</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C147" s="19" t="s">
         <v>324</v>
@@ -8027,13 +8027,13 @@
         <v>26</v>
       </c>
       <c r="F147" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H147" s="20" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8041,7 +8041,7 @@
         <v>325</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C148" s="14" t="s">
         <v>326</v>
@@ -8053,13 +8053,13 @@
         <v>26</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8067,7 +8067,7 @@
         <v>327</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C149" s="19" t="s">
         <v>328</v>
@@ -8079,13 +8079,13 @@
         <v>26</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H149" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>329</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C150" s="14" t="s">
         <v>330</v>
@@ -8105,13 +8105,13 @@
         <v>26</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H150" s="15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8119,7 +8119,7 @@
         <v>331</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C151" s="19" t="s">
         <v>332</v>
@@ -8131,13 +8131,13 @@
         <v>26</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H151" s="20" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8157,10 +8157,10 @@
         <v>26</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H152" s="15" t="s">
         <v>13</v>
@@ -8183,10 +8183,10 @@
         <v>26</v>
       </c>
       <c r="F153" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>13</v>
@@ -8209,10 +8209,10 @@
         <v>26</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>13</v>
@@ -8235,10 +8235,10 @@
         <v>26</v>
       </c>
       <c r="F155" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H155" s="20" t="s">
         <v>13</v>
@@ -8261,10 +8261,10 @@
         <v>26</v>
       </c>
       <c r="F156" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H156" s="15" t="s">
         <v>13</v>
@@ -8287,10 +8287,10 @@
         <v>26</v>
       </c>
       <c r="F157" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>13</v>
@@ -8313,10 +8313,10 @@
         <v>26</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H158" s="15" t="s">
         <v>13</v>
@@ -8339,10 +8339,10 @@
         <v>26</v>
       </c>
       <c r="F159" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>13</v>
@@ -8365,10 +8365,10 @@
         <v>26</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H160" s="15" t="s">
         <v>13</v>
@@ -8391,10 +8391,10 @@
         <v>26</v>
       </c>
       <c r="F161" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H161" s="20" t="s">
         <v>13</v>
@@ -8417,10 +8417,10 @@
         <v>26</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>13</v>
@@ -8443,10 +8443,10 @@
         <v>26</v>
       </c>
       <c r="F163" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H163" s="20" t="s">
         <v>13</v>
@@ -8469,10 +8469,10 @@
         <v>26</v>
       </c>
       <c r="F164" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H164" s="15" t="s">
         <v>13</v>
@@ -8495,10 +8495,10 @@
         <v>26</v>
       </c>
       <c r="F165" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H165" s="20" t="s">
         <v>13</v>
@@ -8521,10 +8521,10 @@
         <v>26</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H166" s="15" t="s">
         <v>13</v>
@@ -8547,10 +8547,10 @@
         <v>26</v>
       </c>
       <c r="F167" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G167" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H167" s="20" t="s">
         <v>13</v>
@@ -8573,10 +8573,10 @@
         <v>26</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H168" s="15" t="s">
         <v>13</v>
@@ -8599,10 +8599,10 @@
         <v>26</v>
       </c>
       <c r="F169" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H169" s="20" t="s">
         <v>13</v>
@@ -8625,10 +8625,10 @@
         <v>26</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H170" s="15" t="s">
         <v>13</v>
@@ -8651,10 +8651,10 @@
         <v>26</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G171" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H171" s="20" t="s">
         <v>13</v>
@@ -8677,10 +8677,10 @@
         <v>26</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H172" s="15" t="s">
         <v>13</v>
@@ -8703,10 +8703,10 @@
         <v>26</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G173" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H173" s="20" t="s">
         <v>13</v>
@@ -8729,10 +8729,10 @@
         <v>26</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H174" s="15" t="s">
         <v>13</v>
@@ -8755,10 +8755,10 @@
         <v>26</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G175" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H175" s="20" t="s">
         <v>13</v>
@@ -8781,10 +8781,10 @@
         <v>26</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H176" s="15" t="s">
         <v>13</v>
@@ -8807,10 +8807,10 @@
         <v>26</v>
       </c>
       <c r="F177" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G177" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H177" s="20" t="s">
         <v>13</v>
@@ -8833,10 +8833,10 @@
         <v>26</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H178" s="15" t="s">
         <v>13</v>
@@ -8859,10 +8859,10 @@
         <v>26</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G179" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H179" s="20" t="s">
         <v>13</v>
@@ -8885,13 +8885,13 @@
         <v>26</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H180" s="15" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -8911,10 +8911,10 @@
         <v>26</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H181" s="20" t="s">
         <v>13</v>
@@ -8937,10 +8937,10 @@
         <v>26</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H182" s="15" t="s">
         <v>13</v>
@@ -8963,10 +8963,10 @@
         <v>26</v>
       </c>
       <c r="F183" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H183" s="20" t="s">
         <v>13</v>
@@ -8989,10 +8989,10 @@
         <v>26</v>
       </c>
       <c r="F184" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H184" s="15" t="s">
         <v>13</v>
@@ -9015,10 +9015,10 @@
         <v>26</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H185" s="20" t="s">
         <v>13</v>
@@ -9041,10 +9041,10 @@
         <v>26</v>
       </c>
       <c r="F186" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H186" s="15" t="s">
         <v>13</v>
@@ -9067,10 +9067,10 @@
         <v>26</v>
       </c>
       <c r="F187" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H187" s="20" t="s">
         <v>13</v>
@@ -9093,10 +9093,10 @@
         <v>26</v>
       </c>
       <c r="F188" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H188" s="15" t="s">
         <v>13</v>
@@ -9119,10 +9119,10 @@
         <v>26</v>
       </c>
       <c r="F189" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H189" s="20" t="s">
         <v>13</v>
@@ -9145,10 +9145,10 @@
         <v>26</v>
       </c>
       <c r="F190" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H190" s="15" t="s">
         <v>13</v>
@@ -9171,10 +9171,10 @@
         <v>26</v>
       </c>
       <c r="F191" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H191" s="20" t="s">
         <v>13</v>
@@ -9197,10 +9197,10 @@
         <v>26</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H192" s="15" t="s">
         <v>13</v>
@@ -9223,10 +9223,10 @@
         <v>26</v>
       </c>
       <c r="F193" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H193" s="20" t="s">
         <v>13</v>
@@ -9249,10 +9249,10 @@
         <v>26</v>
       </c>
       <c r="F194" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H194" s="15" t="s">
         <v>13</v>
@@ -9275,10 +9275,10 @@
         <v>26</v>
       </c>
       <c r="F195" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H195" s="20" t="s">
         <v>13</v>
@@ -9301,10 +9301,10 @@
         <v>26</v>
       </c>
       <c r="F196" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H196" s="15" t="s">
         <v>13</v>
@@ -9327,10 +9327,10 @@
         <v>26</v>
       </c>
       <c r="F197" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H197" s="20" t="s">
         <v>13</v>
@@ -9353,10 +9353,10 @@
         <v>26</v>
       </c>
       <c r="F198" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>13</v>
@@ -9379,10 +9379,10 @@
         <v>26</v>
       </c>
       <c r="F199" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H199" s="20" t="s">
         <v>13</v>
@@ -9405,10 +9405,10 @@
         <v>26</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H200" s="15" t="s">
         <v>13</v>
@@ -9431,10 +9431,10 @@
         <v>26</v>
       </c>
       <c r="F201" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G201" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H201" s="20" t="s">
         <v>13</v>
@@ -9457,10 +9457,10 @@
         <v>26</v>
       </c>
       <c r="F202" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>13</v>
@@ -9483,10 +9483,10 @@
         <v>26</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H203" s="20" t="s">
         <v>13</v>
@@ -9509,10 +9509,10 @@
         <v>26</v>
       </c>
       <c r="F204" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H204" s="15" t="s">
         <v>13</v>
@@ -9535,10 +9535,10 @@
         <v>26</v>
       </c>
       <c r="F205" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G205" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H205" s="20" t="s">
         <v>13</v>
@@ -9561,10 +9561,10 @@
         <v>26</v>
       </c>
       <c r="F206" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G206" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H206" s="15" t="s">
         <v>13</v>
@@ -9587,10 +9587,10 @@
         <v>26</v>
       </c>
       <c r="F207" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G207" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H207" s="20" t="s">
         <v>13</v>
@@ -9613,10 +9613,10 @@
         <v>26</v>
       </c>
       <c r="F208" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G208" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H208" s="15" t="s">
         <v>13</v>
@@ -9639,10 +9639,10 @@
         <v>26</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H209" s="20" t="s">
         <v>13</v>
@@ -9665,10 +9665,10 @@
         <v>26</v>
       </c>
       <c r="F210" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>13</v>
@@ -9691,10 +9691,10 @@
         <v>26</v>
       </c>
       <c r="F211" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G211" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H211" s="20" t="s">
         <v>13</v>
@@ -9717,10 +9717,10 @@
         <v>26</v>
       </c>
       <c r="F212" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H212" s="15" t="s">
         <v>13</v>
@@ -9743,10 +9743,10 @@
         <v>26</v>
       </c>
       <c r="F213" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H213" s="20" t="s">
         <v>13</v>
@@ -9769,10 +9769,10 @@
         <v>26</v>
       </c>
       <c r="F214" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G214" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H214" s="15" t="s">
         <v>13</v>
@@ -9795,10 +9795,10 @@
         <v>26</v>
       </c>
       <c r="F215" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H215" s="20" t="s">
         <v>13</v>
@@ -9821,10 +9821,10 @@
         <v>26</v>
       </c>
       <c r="F216" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G216" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H216" s="15" t="s">
         <v>13</v>
@@ -9847,10 +9847,10 @@
         <v>26</v>
       </c>
       <c r="F217" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H217" s="20" t="s">
         <v>13</v>
@@ -9873,10 +9873,10 @@
         <v>26</v>
       </c>
       <c r="F218" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H218" s="15" t="s">
         <v>13</v>
@@ -9899,10 +9899,10 @@
         <v>26</v>
       </c>
       <c r="F219" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H219" s="20" t="s">
         <v>13</v>
@@ -9925,10 +9925,10 @@
         <v>26</v>
       </c>
       <c r="F220" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H220" s="15" t="s">
         <v>13</v>
@@ -9951,10 +9951,10 @@
         <v>26</v>
       </c>
       <c r="F221" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H221" s="20" t="s">
         <v>13</v>
@@ -9977,10 +9977,10 @@
         <v>26</v>
       </c>
       <c r="F222" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>13</v>
@@ -10003,10 +10003,10 @@
         <v>26</v>
       </c>
       <c r="F223" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G223" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H223" s="20" t="s">
         <v>13</v>
@@ -10029,10 +10029,10 @@
         <v>26</v>
       </c>
       <c r="F224" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G224" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H224" s="15" t="s">
         <v>13</v>
@@ -10055,10 +10055,10 @@
         <v>26</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H225" s="20" t="s">
         <v>13</v>
@@ -10081,10 +10081,10 @@
         <v>26</v>
       </c>
       <c r="F226" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G226" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H226" s="15" t="s">
         <v>13</v>
@@ -10107,10 +10107,10 @@
         <v>26</v>
       </c>
       <c r="F227" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H227" s="20" t="s">
         <v>13</v>
@@ -10133,10 +10133,10 @@
         <v>26</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G228" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H228" s="15" t="s">
         <v>13</v>
@@ -10159,10 +10159,10 @@
         <v>26</v>
       </c>
       <c r="F229" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G229" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H229" s="20" t="s">
         <v>13</v>
@@ -10185,10 +10185,10 @@
         <v>26</v>
       </c>
       <c r="F230" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G230" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H230" s="15" t="s">
         <v>13</v>
@@ -10211,10 +10211,10 @@
         <v>26</v>
       </c>
       <c r="F231" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G231" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H231" s="20" t="s">
         <v>13</v>
@@ -10237,10 +10237,10 @@
         <v>26</v>
       </c>
       <c r="F232" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H232" s="15" t="s">
         <v>13</v>
@@ -10263,10 +10263,10 @@
         <v>26</v>
       </c>
       <c r="F233" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G233" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H233" s="20" t="s">
         <v>13</v>
@@ -10289,10 +10289,10 @@
         <v>26</v>
       </c>
       <c r="F234" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H234" s="15" t="s">
         <v>13</v>
@@ -10315,10 +10315,10 @@
         <v>26</v>
       </c>
       <c r="F235" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G235" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H235" s="20" t="s">
         <v>13</v>
@@ -10341,10 +10341,10 @@
         <v>26</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G236" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H236" s="15" t="s">
         <v>13</v>
@@ -10367,10 +10367,10 @@
         <v>26</v>
       </c>
       <c r="F237" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G237" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H237" s="20" t="s">
         <v>13</v>
@@ -10393,10 +10393,10 @@
         <v>26</v>
       </c>
       <c r="F238" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G238" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H238" s="15" t="s">
         <v>13</v>
@@ -10419,10 +10419,10 @@
         <v>26</v>
       </c>
       <c r="F239" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G239" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H239" s="20" t="s">
         <v>13</v>
@@ -10445,10 +10445,10 @@
         <v>26</v>
       </c>
       <c r="F240" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G240" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H240" s="15" t="s">
         <v>13</v>
@@ -10471,10 +10471,10 @@
         <v>26</v>
       </c>
       <c r="F241" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G241" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H241" s="20" t="s">
         <v>13</v>
@@ -10497,10 +10497,10 @@
         <v>26</v>
       </c>
       <c r="F242" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G242" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H242" s="15" t="s">
         <v>13</v>
@@ -10523,10 +10523,10 @@
         <v>26</v>
       </c>
       <c r="F243" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G243" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H243" s="20" t="s">
         <v>13</v>
@@ -10549,10 +10549,10 @@
         <v>26</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G244" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H244" s="15" t="s">
         <v>13</v>
@@ -10575,10 +10575,10 @@
         <v>26</v>
       </c>
       <c r="F245" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G245" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H245" s="20" t="s">
         <v>13</v>
@@ -10601,10 +10601,10 @@
         <v>26</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G246" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H246" s="15" t="s">
         <v>13</v>
@@ -10627,10 +10627,10 @@
         <v>26</v>
       </c>
       <c r="F247" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G247" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H247" s="20" t="s">
         <v>13</v>
@@ -10653,10 +10653,10 @@
         <v>26</v>
       </c>
       <c r="F248" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G248" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H248" s="15" t="s">
         <v>13</v>
@@ -10679,10 +10679,10 @@
         <v>26</v>
       </c>
       <c r="F249" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G249" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H249" s="20" t="s">
         <v>13</v>
@@ -10705,10 +10705,10 @@
         <v>26</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G250" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H250" s="15" t="s">
         <v>13</v>
@@ -10731,10 +10731,10 @@
         <v>26</v>
       </c>
       <c r="F251" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G251" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H251" s="20" t="s">
         <v>13</v>
@@ -10757,10 +10757,10 @@
         <v>26</v>
       </c>
       <c r="F252" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G252" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H252" s="15" t="s">
         <v>13</v>
@@ -10783,10 +10783,10 @@
         <v>26</v>
       </c>
       <c r="F253" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H253" s="20" t="s">
         <v>13</v>
@@ -10809,10 +10809,10 @@
         <v>26</v>
       </c>
       <c r="F254" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G254" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H254" s="15" t="s">
         <v>13</v>
@@ -10835,10 +10835,10 @@
         <v>26</v>
       </c>
       <c r="F255" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G255" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H255" s="20" t="s">
         <v>13</v>
@@ -10861,10 +10861,10 @@
         <v>26</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G256" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H256" s="15" t="s">
         <v>13</v>
@@ -10887,10 +10887,10 @@
         <v>26</v>
       </c>
       <c r="F257" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G257" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H257" s="20" t="s">
         <v>13</v>
@@ -10913,10 +10913,10 @@
         <v>26</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G258" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H258" s="15" t="s">
         <v>13</v>
@@ -10939,10 +10939,10 @@
         <v>26</v>
       </c>
       <c r="F259" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G259" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H259" s="20" t="s">
         <v>13</v>
@@ -10965,10 +10965,10 @@
         <v>26</v>
       </c>
       <c r="F260" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G260" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H260" s="15" t="s">
         <v>13</v>
@@ -10991,10 +10991,10 @@
         <v>26</v>
       </c>
       <c r="F261" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G261" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H261" s="20" t="s">
         <v>13</v>
@@ -11017,10 +11017,10 @@
         <v>26</v>
       </c>
       <c r="F262" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G262" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H262" s="15" t="s">
         <v>13</v>
@@ -11043,10 +11043,10 @@
         <v>26</v>
       </c>
       <c r="F263" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G263" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H263" s="20" t="s">
         <v>13</v>
@@ -11069,10 +11069,10 @@
         <v>26</v>
       </c>
       <c r="F264" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G264" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H264" s="15" t="s">
         <v>13</v>
@@ -11095,10 +11095,10 @@
         <v>26</v>
       </c>
       <c r="F265" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G265" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H265" s="20" t="s">
         <v>13</v>
@@ -11121,10 +11121,10 @@
         <v>26</v>
       </c>
       <c r="F266" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G266" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H266" s="15" t="s">
         <v>13</v>
@@ -11147,10 +11147,10 @@
         <v>26</v>
       </c>
       <c r="F267" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G267" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H267" s="20" t="s">
         <v>13</v>
@@ -11173,10 +11173,10 @@
         <v>26</v>
       </c>
       <c r="F268" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G268" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H268" s="15" t="s">
         <v>13</v>
@@ -11199,10 +11199,10 @@
         <v>26</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G269" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H269" s="20" t="s">
         <v>13</v>
@@ -11225,10 +11225,10 @@
         <v>26</v>
       </c>
       <c r="F270" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G270" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H270" s="15" t="s">
         <v>13</v>
@@ -11251,10 +11251,10 @@
         <v>26</v>
       </c>
       <c r="F271" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G271" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H271" s="20" t="s">
         <v>13</v>
@@ -11277,10 +11277,10 @@
         <v>26</v>
       </c>
       <c r="F272" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G272" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H272" s="15" t="s">
         <v>13</v>
@@ -11303,10 +11303,10 @@
         <v>26</v>
       </c>
       <c r="F273" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G273" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H273" s="20" t="s">
         <v>13</v>
@@ -11329,10 +11329,10 @@
         <v>26</v>
       </c>
       <c r="F274" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G274" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H274" s="15" t="s">
         <v>13</v>
@@ -11355,10 +11355,10 @@
         <v>26</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G275" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H275" s="20" t="s">
         <v>13</v>
@@ -11381,10 +11381,10 @@
         <v>26</v>
       </c>
       <c r="F276" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G276" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H276" s="15" t="s">
         <v>13</v>
@@ -11407,10 +11407,10 @@
         <v>26</v>
       </c>
       <c r="F277" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G277" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H277" s="20" t="s">
         <v>13</v>
@@ -11433,10 +11433,10 @@
         <v>26</v>
       </c>
       <c r="F278" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G278" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H278" s="15" t="s">
         <v>13</v>
@@ -11459,10 +11459,10 @@
         <v>26</v>
       </c>
       <c r="F279" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G279" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H279" s="20" t="s">
         <v>13</v>
@@ -11485,10 +11485,10 @@
         <v>26</v>
       </c>
       <c r="F280" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G280" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H280" s="15" t="s">
         <v>13</v>
@@ -11511,10 +11511,10 @@
         <v>26</v>
       </c>
       <c r="F281" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G281" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H281" s="20" t="s">
         <v>13</v>
@@ -11537,10 +11537,10 @@
         <v>26</v>
       </c>
       <c r="F282" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G282" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H282" s="15" t="s">
         <v>13</v>
@@ -11563,10 +11563,10 @@
         <v>26</v>
       </c>
       <c r="F283" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G283" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H283" s="20" t="s">
         <v>13</v>
@@ -11589,10 +11589,10 @@
         <v>26</v>
       </c>
       <c r="F284" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G284" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H284" s="15" t="s">
         <v>13</v>
@@ -11615,10 +11615,10 @@
         <v>26</v>
       </c>
       <c r="F285" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G285" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H285" s="20" t="s">
         <v>13</v>
@@ -11641,10 +11641,10 @@
         <v>26</v>
       </c>
       <c r="F286" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G286" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H286" s="15" t="s">
         <v>13</v>
@@ -11667,10 +11667,10 @@
         <v>26</v>
       </c>
       <c r="F287" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G287" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H287" s="20" t="s">
         <v>13</v>
@@ -11693,10 +11693,10 @@
         <v>26</v>
       </c>
       <c r="F288" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G288" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H288" s="15" t="s">
         <v>13</v>
@@ -11719,10 +11719,10 @@
         <v>26</v>
       </c>
       <c r="F289" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G289" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H289" s="20" t="s">
         <v>13</v>
@@ -11745,10 +11745,10 @@
         <v>26</v>
       </c>
       <c r="F290" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G290" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H290" s="15" t="s">
         <v>13</v>
@@ -11771,10 +11771,10 @@
         <v>26</v>
       </c>
       <c r="F291" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G291" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H291" s="20" t="s">
         <v>13</v>
@@ -11797,10 +11797,10 @@
         <v>26</v>
       </c>
       <c r="F292" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G292" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H292" s="15" t="s">
         <v>13</v>
@@ -11823,10 +11823,10 @@
         <v>26</v>
       </c>
       <c r="F293" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G293" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H293" s="20" t="s">
         <v>13</v>
@@ -11849,10 +11849,10 @@
         <v>26</v>
       </c>
       <c r="F294" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G294" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H294" s="15" t="s">
         <v>13</v>
@@ -11875,10 +11875,10 @@
         <v>26</v>
       </c>
       <c r="F295" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G295" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H295" s="20" t="s">
         <v>13</v>
@@ -11901,10 +11901,10 @@
         <v>26</v>
       </c>
       <c r="F296" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G296" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H296" s="15" t="s">
         <v>13</v>
@@ -11927,10 +11927,10 @@
         <v>26</v>
       </c>
       <c r="F297" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G297" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H297" s="20" t="s">
         <v>13</v>
@@ -11953,10 +11953,10 @@
         <v>26</v>
       </c>
       <c r="F298" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G298" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H298" s="15" t="s">
         <v>13</v>
@@ -11979,10 +11979,10 @@
         <v>26</v>
       </c>
       <c r="F299" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G299" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H299" s="20" t="s">
         <v>13</v>
@@ -12005,10 +12005,10 @@
         <v>26</v>
       </c>
       <c r="F300" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G300" s="15" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H300" s="15" t="s">
         <v>13</v>
@@ -12031,10 +12031,10 @@
         <v>26</v>
       </c>
       <c r="F301" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="G301" s="20" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="H301" s="20" t="s">
         <v>13</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B80" s="24" t="s">
         <v>807</v>
@@ -13472,7 +13472,7 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>809</v>
@@ -13489,7 +13489,7 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B82" s="24" t="s">
         <v>811</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>813</v>
@@ -13523,7 +13523,7 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="24" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B84" s="24" t="s">
         <v>815</v>
@@ -13540,7 +13540,7 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>817</v>
@@ -13557,7 +13557,7 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B86" s="24" t="s">
         <v>819</v>
@@ -13574,7 +13574,7 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>821</v>
@@ -13591,7 +13591,7 @@
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="B88" s="24" t="s">
         <v>823</v>
@@ -13608,7 +13608,7 @@
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>825</v>
@@ -13625,7 +13625,7 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B90" s="24" t="s">
         <v>827</v>
@@ -13642,7 +13642,7 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>829</v>
@@ -13659,7 +13659,7 @@
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B92" s="24" t="s">
         <v>831</v>
@@ -13676,7 +13676,7 @@
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>833</v>
@@ -13693,7 +13693,7 @@
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B94" s="24" t="s">
         <v>835</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>837</v>
@@ -13727,7 +13727,7 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B96" s="24" t="s">
         <v>839</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>841</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B98" s="24" t="s">
         <v>843</v>
@@ -13778,7 +13778,7 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>845</v>
@@ -13795,7 +13795,7 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B100" s="24" t="s">
         <v>847</v>
@@ -13812,7 +13812,7 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>849</v>
@@ -13829,7 +13829,7 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B102" s="24" t="s">
         <v>851</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>854</v>
@@ -13863,7 +13863,7 @@
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B104" s="24" t="s">
         <v>856</v>
@@ -13880,7 +13880,7 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>858</v>
@@ -13897,7 +13897,7 @@
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B106" s="24" t="s">
         <v>860</v>
@@ -13914,7 +13914,7 @@
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>862</v>
@@ -13931,7 +13931,7 @@
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B108" s="24" t="s">
         <v>864</v>
@@ -13948,7 +13948,7 @@
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>866</v>
@@ -13965,7 +13965,7 @@
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B110" s="24" t="s">
         <v>868</v>
@@ -13982,7 +13982,7 @@
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>870</v>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B112" s="24" t="s">
         <v>872</v>
@@ -14016,7 +14016,7 @@
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>874</v>
@@ -14033,7 +14033,7 @@
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B114" s="24" t="s">
         <v>876</v>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B115" s="26" t="s">
         <v>878</v>
@@ -14067,7 +14067,7 @@
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B116" s="24" t="s">
         <v>880</v>
@@ -14084,7 +14084,7 @@
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>882</v>
@@ -14101,7 +14101,7 @@
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B118" s="24" t="s">
         <v>884</v>
@@ -14118,7 +14118,7 @@
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>886</v>
@@ -14135,7 +14135,7 @@
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="24" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B120" s="24" t="s">
         <v>888</v>
@@ -14152,7 +14152,7 @@
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B121" s="26" t="s">
         <v>890</v>
@@ -14169,7 +14169,7 @@
     </row>
     <row r="122" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B122" s="24" t="s">
         <v>892</v>
@@ -14186,7 +14186,7 @@
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B123" s="26" t="s">
         <v>894</v>
@@ -14203,7 +14203,7 @@
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B124" s="24" t="s">
         <v>896</v>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B125" s="26" t="s">
         <v>898</v>
@@ -14237,7 +14237,7 @@
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B126" s="24" t="s">
         <v>900</v>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>902</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B128" s="24" t="s">
         <v>904</v>
@@ -14288,7 +14288,7 @@
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>906</v>
@@ -14305,7 +14305,7 @@
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B130" s="24" t="s">
         <v>908</v>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B131" s="26" t="s">
         <v>910</v>
@@ -14339,7 +14339,7 @@
     </row>
     <row r="132" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B132" s="24" t="s">
         <v>912</v>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="133" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B133" s="26" t="s">
         <v>914</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="134" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>916</v>
@@ -14390,7 +14390,7 @@
     </row>
     <row r="135" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B135" s="26" t="s">
         <v>918</v>
@@ -14407,7 +14407,7 @@
     </row>
     <row r="136" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>920</v>
@@ -14424,7 +14424,7 @@
     </row>
     <row r="137" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B137" s="26" t="s">
         <v>922</v>
@@ -14441,7 +14441,7 @@
     </row>
     <row r="138" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B138" s="24" t="s">
         <v>924</v>
@@ -14458,7 +14458,7 @@
     </row>
     <row r="139" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B139" s="26" t="s">
         <v>926</v>
@@ -14475,7 +14475,7 @@
     </row>
     <row r="140" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B140" s="24" t="s">
         <v>928</v>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="141" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B141" s="26" t="s">
         <v>930</v>
@@ -14509,7 +14509,7 @@
     </row>
     <row r="142" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B142" s="24" t="s">
         <v>932</v>
@@ -14526,7 +14526,7 @@
     </row>
     <row r="143" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B143" s="26" t="s">
         <v>934</v>
@@ -14543,7 +14543,7 @@
     </row>
     <row r="144" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B144" s="24" t="s">
         <v>936</v>
@@ -14560,7 +14560,7 @@
     </row>
     <row r="145" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B145" s="26" t="s">
         <v>938</v>
@@ -14577,7 +14577,7 @@
     </row>
     <row r="146" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B146" s="24" t="s">
         <v>940</v>
@@ -14594,7 +14594,7 @@
     </row>
     <row r="147" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B147" s="26" t="s">
         <v>942</v>
@@ -14611,7 +14611,7 @@
     </row>
     <row r="148" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B148" s="24" t="s">
         <v>944</v>
@@ -14628,7 +14628,7 @@
     </row>
     <row r="149" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B149" s="26" t="s">
         <v>946</v>
@@ -14645,7 +14645,7 @@
     </row>
     <row r="150" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B150" s="24" t="s">
         <v>948</v>
@@ -14662,7 +14662,7 @@
     </row>
     <row r="151" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B151" s="26" t="s">
         <v>950</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="152" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B152" s="24" t="s">
         <v>952</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="153" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B153" s="26" t="s">
         <v>955</v>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="154" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B154" s="24" t="s">
         <v>957</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="155" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B155" s="26" t="s">
         <v>959</v>
@@ -14747,7 +14747,7 @@
     </row>
     <row r="156" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B156" s="24" t="s">
         <v>961</v>
@@ -14764,7 +14764,7 @@
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B157" s="26" t="s">
         <v>963</v>
@@ -14781,7 +14781,7 @@
     </row>
     <row r="158" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B158" s="24" t="s">
         <v>965</v>
@@ -14798,7 +14798,7 @@
     </row>
     <row r="159" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B159" s="26" t="s">
         <v>967</v>
@@ -14815,7 +14815,7 @@
     </row>
     <row r="160" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B160" s="24" t="s">
         <v>969</v>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="161" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B161" s="26" t="s">
         <v>971</v>
@@ -14849,7 +14849,7 @@
     </row>
     <row r="162" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B162" s="24" t="s">
         <v>973</v>
@@ -14866,7 +14866,7 @@
     </row>
     <row r="163" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B163" s="26" t="s">
         <v>975</v>
@@ -14883,7 +14883,7 @@
     </row>
     <row r="164" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B164" s="24" t="s">
         <v>977</v>
@@ -14900,7 +14900,7 @@
     </row>
     <row r="165" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B165" s="26" t="s">
         <v>979</v>
@@ -14917,7 +14917,7 @@
     </row>
     <row r="166" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B166" s="24" t="s">
         <v>981</v>
@@ -14934,7 +14934,7 @@
     </row>
     <row r="167" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B167" s="26" t="s">
         <v>983</v>
@@ -14951,7 +14951,7 @@
     </row>
     <row r="168" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B168" s="24" t="s">
         <v>985</v>
@@ -14968,7 +14968,7 @@
     </row>
     <row r="169" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B169" s="26" t="s">
         <v>987</v>
@@ -14985,7 +14985,7 @@
     </row>
     <row r="170" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B170" s="24" t="s">
         <v>989</v>
@@ -15002,7 +15002,7 @@
     </row>
     <row r="171" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B171" s="26" t="s">
         <v>991</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="172" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B172" s="24" t="s">
         <v>993</v>
@@ -15036,7 +15036,7 @@
     </row>
     <row r="173" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B173" s="26" t="s">
         <v>995</v>
@@ -15053,7 +15053,7 @@
     </row>
     <row r="174" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B174" s="24" t="s">
         <v>997</v>
@@ -15070,7 +15070,7 @@
     </row>
     <row r="175" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B175" s="26" t="s">
         <v>999</v>
@@ -15087,7 +15087,7 @@
     </row>
     <row r="176" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B176" s="24" t="s">
         <v>1001</v>
@@ -15104,7 +15104,7 @@
     </row>
     <row r="177" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B177" s="26" t="s">
         <v>1003</v>
@@ -15121,7 +15121,7 @@
     </row>
     <row r="178" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B178" s="24" t="s">
         <v>1005</v>
@@ -15138,7 +15138,7 @@
     </row>
     <row r="179" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B179" s="26" t="s">
         <v>1007</v>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="180" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B180" s="24" t="s">
         <v>1009</v>
@@ -15172,7 +15172,7 @@
     </row>
     <row r="181" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B181" s="26" t="s">
         <v>1011</v>
@@ -15189,7 +15189,7 @@
     </row>
     <row r="182" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B182" s="24" t="s">
         <v>1013</v>
@@ -15206,7 +15206,7 @@
     </row>
     <row r="183" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B183" s="26" t="s">
         <v>1015</v>
@@ -15223,7 +15223,7 @@
     </row>
     <row r="184" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B184" s="24" t="s">
         <v>1017</v>
@@ -15240,7 +15240,7 @@
     </row>
     <row r="185" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B185" s="26" t="s">
         <v>1019</v>
@@ -15257,7 +15257,7 @@
     </row>
     <row r="186" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B186" s="24" t="s">
         <v>1021</v>
@@ -15274,7 +15274,7 @@
     </row>
     <row r="187" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B187" s="26" t="s">
         <v>1023</v>
@@ -15291,7 +15291,7 @@
     </row>
     <row r="188" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B188" s="24" t="s">
         <v>1025</v>
@@ -15308,7 +15308,7 @@
     </row>
     <row r="189" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B189" s="26" t="s">
         <v>1027</v>
@@ -15325,7 +15325,7 @@
     </row>
     <row r="190" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B190" s="24" t="s">
         <v>1029</v>
@@ -15342,7 +15342,7 @@
     </row>
     <row r="191" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B191" s="26" t="s">
         <v>1031</v>
@@ -15359,7 +15359,7 @@
     </row>
     <row r="192" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B192" s="24" t="s">
         <v>1033</v>
@@ -15376,7 +15376,7 @@
     </row>
     <row r="193" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B193" s="26" t="s">
         <v>1035</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="194" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B194" s="24" t="s">
         <v>1037</v>
@@ -15410,7 +15410,7 @@
     </row>
     <row r="195" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B195" s="26" t="s">
         <v>1039</v>
@@ -15427,7 +15427,7 @@
     </row>
     <row r="196" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B196" s="24" t="s">
         <v>1041</v>
@@ -15444,7 +15444,7 @@
     </row>
     <row r="197" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B197" s="26" t="s">
         <v>1043</v>
@@ -15461,7 +15461,7 @@
     </row>
     <row r="198" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B198" s="24" t="s">
         <v>1045</v>
@@ -15478,7 +15478,7 @@
     </row>
     <row r="199" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B199" s="26" t="s">
         <v>1047</v>
@@ -15495,7 +15495,7 @@
     </row>
     <row r="200" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B200" s="24" t="s">
         <v>1049</v>
@@ -15512,7 +15512,7 @@
     </row>
     <row r="201" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B201" s="26" t="s">
         <v>1051</v>
@@ -15529,7 +15529,7 @@
     </row>
     <row r="202" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B202" s="24" t="s">
         <v>1053</v>
@@ -15546,7 +15546,7 @@
     </row>
     <row r="203" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B203" s="26" t="s">
         <v>1056</v>
@@ -15563,7 +15563,7 @@
     </row>
     <row r="204" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B204" s="24" t="s">
         <v>1058</v>
@@ -15580,7 +15580,7 @@
     </row>
     <row r="205" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B205" s="26" t="s">
         <v>1060</v>
@@ -15597,7 +15597,7 @@
     </row>
     <row r="206" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B206" s="24" t="s">
         <v>1062</v>
@@ -15614,7 +15614,7 @@
     </row>
     <row r="207" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B207" s="26" t="s">
         <v>1064</v>
@@ -15631,7 +15631,7 @@
     </row>
     <row r="208" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B208" s="24" t="s">
         <v>1066</v>
@@ -15648,7 +15648,7 @@
     </row>
     <row r="209" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B209" s="26" t="s">
         <v>1068</v>
@@ -15665,7 +15665,7 @@
     </row>
     <row r="210" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B210" s="24" t="s">
         <v>1070</v>
@@ -15682,7 +15682,7 @@
     </row>
     <row r="211" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B211" s="26" t="s">
         <v>1072</v>
@@ -15699,7 +15699,7 @@
     </row>
     <row r="212" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B212" s="24" t="s">
         <v>1074</v>
@@ -15716,7 +15716,7 @@
     </row>
     <row r="213" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B213" s="26" t="s">
         <v>1076</v>
@@ -15733,7 +15733,7 @@
     </row>
     <row r="214" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B214" s="24" t="s">
         <v>1078</v>
@@ -15750,7 +15750,7 @@
     </row>
     <row r="215" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B215" s="26" t="s">
         <v>1080</v>
@@ -15767,7 +15767,7 @@
     </row>
     <row r="216" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B216" s="24" t="s">
         <v>1082</v>
@@ -15784,7 +15784,7 @@
     </row>
     <row r="217" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B217" s="26" t="s">
         <v>1084</v>
@@ -15801,7 +15801,7 @@
     </row>
     <row r="218" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B218" s="24" t="s">
         <v>1086</v>
@@ -15818,7 +15818,7 @@
     </row>
     <row r="219" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B219" s="26" t="s">
         <v>1088</v>
@@ -15835,7 +15835,7 @@
     </row>
     <row r="220" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B220" s="24" t="s">
         <v>1090</v>
@@ -15852,7 +15852,7 @@
     </row>
     <row r="221" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B221" s="26" t="s">
         <v>1092</v>
@@ -15869,7 +15869,7 @@
     </row>
     <row r="222" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B222" s="24" t="s">
         <v>1094</v>
@@ -15886,7 +15886,7 @@
     </row>
     <row r="223" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B223" s="26" t="s">
         <v>1096</v>
@@ -15903,7 +15903,7 @@
     </row>
     <row r="224" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B224" s="24" t="s">
         <v>1098</v>
@@ -15920,7 +15920,7 @@
     </row>
     <row r="225" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B225" s="26" t="s">
         <v>1100</v>
@@ -15937,7 +15937,7 @@
     </row>
     <row r="226" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B226" s="24" t="s">
         <v>1102</v>
@@ -15954,7 +15954,7 @@
     </row>
     <row r="227" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B227" s="26" t="s">
         <v>1104</v>
@@ -15971,7 +15971,7 @@
     </row>
     <row r="228" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B228" s="24" t="s">
         <v>1106</v>
@@ -15988,7 +15988,7 @@
     </row>
     <row r="229" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B229" s="26" t="s">
         <v>1108</v>
@@ -16005,7 +16005,7 @@
     </row>
     <row r="230" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B230" s="24" t="s">
         <v>1110</v>
@@ -16022,7 +16022,7 @@
     </row>
     <row r="231" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B231" s="26" t="s">
         <v>1112</v>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="232" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B232" s="24" t="s">
         <v>1114</v>
@@ -16056,7 +16056,7 @@
     </row>
     <row r="233" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B233" s="26" t="s">
         <v>1116</v>
@@ -16073,7 +16073,7 @@
     </row>
     <row r="234" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B234" s="24" t="s">
         <v>1118</v>
@@ -16090,7 +16090,7 @@
     </row>
     <row r="235" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B235" s="26" t="s">
         <v>1120</v>
@@ -16107,7 +16107,7 @@
     </row>
     <row r="236" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B236" s="24" t="s">
         <v>1122</v>
@@ -16124,7 +16124,7 @@
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B237" s="26" t="s">
         <v>1124</v>
@@ -16141,7 +16141,7 @@
     </row>
     <row r="238" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B238" s="24" t="s">
         <v>1126</v>
@@ -16158,7 +16158,7 @@
     </row>
     <row r="239" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B239" s="26" t="s">
         <v>1128</v>
@@ -16175,7 +16175,7 @@
     </row>
     <row r="240" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B240" s="24" t="s">
         <v>1130</v>
@@ -16192,7 +16192,7 @@
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B241" s="26" t="s">
         <v>1132</v>
@@ -16209,7 +16209,7 @@
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B242" s="24" t="s">
         <v>1134</v>
@@ -16226,7 +16226,7 @@
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B243" s="26" t="s">
         <v>1136</v>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B244" s="24" t="s">
         <v>1138</v>
@@ -16260,7 +16260,7 @@
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B245" s="26" t="s">
         <v>1140</v>
@@ -16277,7 +16277,7 @@
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B246" s="24" t="s">
         <v>1142</v>
@@ -16294,7 +16294,7 @@
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B247" s="26" t="s">
         <v>1144</v>
@@ -16311,7 +16311,7 @@
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B248" s="24" t="s">
         <v>1146</v>
@@ -16328,7 +16328,7 @@
     </row>
     <row r="249" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B249" s="26" t="s">
         <v>1148</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="250" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="24" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B250" s="24" t="s">
         <v>1150</v>
@@ -16362,7 +16362,7 @@
     </row>
     <row r="251" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="26" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="B251" s="26" t="s">
         <v>1152</v>
